--- a/EXECUTIVE_TEAM_AUDIT_REPORT_15_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_15_Oct_2026.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -528,7 +528,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Shashikant Chaudhary</t>
+          <t>Rajesh Maharjan</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
@@ -544,18 +544,36 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="B4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -572,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -628,7 +646,30 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
           <t>100.0%</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -643,12 +684,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -659,10 +701,15 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
@@ -671,27 +718,49 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="6" t="n">
+      <c r="C2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n">
+      <c r="B4" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="4" t="n">
+      <c r="C4" s="4" t="n">
         <v>1</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -705,7 +774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX2"/>
+  <dimension ref="A1:AX3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -718,17 +787,17 @@
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="21" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="27" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="37" customWidth="1" min="19" max="19"/>
     <col width="37" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
@@ -739,13 +808,13 @@
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
-    <col width="22" customWidth="1" min="32" max="32"/>
+    <col width="23" customWidth="1" min="32" max="32"/>
     <col width="29" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="15" customWidth="1" min="38" max="38"/>
+    <col width="16" customWidth="1" min="38" max="38"/>
     <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
@@ -1079,10 +1148,8 @@
           <t>Roshan Shrestha</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
-        <is>
-          <t>9700971170</t>
-        </is>
+      <c r="O2" s="3" t="n">
+        <v>9700971170</v>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
@@ -1158,10 +1225,8 @@
           <t>Video content is Buffering</t>
         </is>
       </c>
-      <c r="AH2" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH2" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI2" s="3" t="inlineStr">
         <is>
@@ -1180,55 +1245,259 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN2" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN2" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO2" s="3" t="inlineStr">
         <is>
           <t>1,15</t>
         </is>
       </c>
-      <c r="AP2" s="3" t="inlineStr">
-        <is>
-          <t>85.33794</t>
-        </is>
+      <c r="AP2" s="3" t="n">
+        <v>85.33794</v>
       </c>
       <c r="AQ2" s="3" t="inlineStr"/>
       <c r="AR2" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS2" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT2" s="3" t="inlineStr">
+        <is>
+          <t>3d 11h 2m</t>
+        </is>
+      </c>
+      <c r="AU2" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV2" s="3" t="inlineStr">
+        <is>
           <t>Case : slow issue   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS2" s="3" t="inlineStr">
+      <c r="AW2" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX2" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 9:29 AM</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>TKT1369287</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>Bishnu Kumar Limbu</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>Bishnu Kumar Limbu</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>9767548750</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 09:29:24 AM</t>
+        </is>
+      </c>
+      <c r="S3" s="3" t="inlineStr"/>
+      <c r="T3" s="3" t="inlineStr"/>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>LTP9767548750</t>
+        </is>
+      </c>
+      <c r="V3" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 03:24:02 PM</t>
+        </is>
+      </c>
+      <c r="W3" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 09:29:24 AM</t>
+        </is>
+      </c>
+      <c r="X3" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y3" s="3" t="inlineStr"/>
+      <c r="Z3" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA3" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB3" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC3" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD3" s="3" t="inlineStr"/>
+      <c r="AE3" s="3" t="inlineStr">
+        <is>
+          <t>near by NSF - Nepal Sports Fellowship (Sports Complex) - Sports complex Bafal Lalitpur, Lalitpur, Ne</t>
+        </is>
+      </c>
+      <c r="AF3" s="3" t="inlineStr">
+        <is>
+          <t>9767548750@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG3" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH3" s="3" t="inlineStr"/>
+      <c r="AI3" s="3" t="inlineStr">
+        <is>
+          <t>14:36 hour</t>
+        </is>
+      </c>
+      <c r="AJ3" s="3" t="inlineStr"/>
+      <c r="AK3" s="3" t="inlineStr"/>
+      <c r="AL3" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM3" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN3" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO3" s="3" t="inlineStr">
+        <is>
+          <t>CDB071</t>
+        </is>
+      </c>
+      <c r="AP3" s="3" t="inlineStr"/>
+      <c r="AQ3" s="3" t="inlineStr"/>
+      <c r="AR3" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS3" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT2" s="3" t="inlineStr">
-        <is>
-          <t>3d 11h 2m</t>
-        </is>
-      </c>
-      <c r="AU2" s="3" t="inlineStr">
+      <c r="AT3" s="3" t="inlineStr">
+        <is>
+          <t>1d 18h 5m</t>
+        </is>
+      </c>
+      <c r="AU3" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV2" s="3" t="inlineStr">
-        <is>
-          <t>Case : slow issue   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="AW2" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="AX2" s="3" t="inlineStr">
-        <is>
-          <t>Shashikant Chaudhary</t>
+      <c r="AV3" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW3" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX3" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_15_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_15_Oct_2026.xlsx
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
@@ -568,10 +568,10 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
@@ -646,7 +646,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -657,10 +657,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
@@ -669,7 +669,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -725,10 +725,10 @@
         <v>1</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -757,10 +757,10 @@
         <v>1</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -774,7 +774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX3"/>
+  <dimension ref="A1:AX4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1360,10 +1360,8 @@
           <t>Bishnu Kumar Limbu</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>9767548750</t>
-        </is>
+      <c r="O3" s="3" t="n">
+        <v>9767548750</v>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
@@ -1453,10 +1451,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN3" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN3" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO3" s="3" t="inlineStr">
         <is>
@@ -1467,37 +1463,241 @@
       <c r="AQ3" s="3" t="inlineStr"/>
       <c r="AR3" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS3" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT3" s="3" t="inlineStr">
+        <is>
+          <t>1d 18h 5m</t>
+        </is>
+      </c>
+      <c r="AU3" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV3" s="3" t="inlineStr">
+        <is>
           <t>Case : Wi-Fi 6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AS3" s="3" t="inlineStr">
+      <c r="AW3" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX3" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 9:46 AM</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>TKT1368592</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Prabin Shrestha</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>Prabin Shrestha</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>9842739192</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr"/>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 09:46:16 AM</t>
+        </is>
+      </c>
+      <c r="S4" s="3" t="inlineStr"/>
+      <c r="T4" s="3" t="inlineStr"/>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>9842739192</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 08:32:42 AM</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 09:46:16 AM</t>
+        </is>
+      </c>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y4" s="3" t="inlineStr"/>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA4" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC4" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD4" s="3" t="inlineStr"/>
+      <c r="AE4" s="3" t="inlineStr">
+        <is>
+          <t>nearby Universal Driving Training Center - Driving school Madhyapur Thimi 44600, Bagmati, Central, N</t>
+        </is>
+      </c>
+      <c r="AF4" s="3" t="inlineStr"/>
+      <c r="AG4" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH4" s="3" t="inlineStr"/>
+      <c r="AI4" s="3" t="inlineStr">
+        <is>
+          <t>20:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ4" s="3" t="inlineStr"/>
+      <c r="AK4" s="3" t="inlineStr"/>
+      <c r="AL4" s="3" t="inlineStr">
+        <is>
+          <t>Sunita Yonjan</t>
+        </is>
+      </c>
+      <c r="AM4" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN4" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO4" s="3" t="inlineStr">
+        <is>
+          <t>3,12</t>
+        </is>
+      </c>
+      <c r="AP4" s="3" t="inlineStr"/>
+      <c r="AQ4" s="3" t="inlineStr"/>
+      <c r="AR4" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT3" s="3" t="inlineStr">
-        <is>
-          <t>1d 18h 5m</t>
-        </is>
-      </c>
-      <c r="AU3" s="3" t="inlineStr">
+      <c r="AT4" s="3" t="inlineStr">
+        <is>
+          <t>2d 1h 13m</t>
+        </is>
+      </c>
+      <c r="AU4" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV3" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wi-Fi 6  has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
-      <c r="AW3" s="3" t="inlineStr">
+      <c r="AV4" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW4" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="AX3" s="3" t="inlineStr">
-        <is>
-          <t>Rajesh Maharjan</t>
+      <c r="AX4" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_15_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_15_Oct_2026.xlsx
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4" s="4" t="n">
         <v>3</v>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -646,30 +646,53 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n">
+      <c r="B4" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="C4" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>66.7%</t>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -684,7 +707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -734,7 +757,7 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>IPTV Remote damage Issue</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -748,19 +771,35 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n">
+      <c r="B5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D4" s="4" t="n">
+      <c r="C5" s="4" t="n">
         <v>3</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -774,7 +813,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX4"/>
+  <dimension ref="A1:AX5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -792,7 +831,7 @@
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="21" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="27" customWidth="1" min="16" max="16"/>
+    <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="37" customWidth="1" min="19" max="19"/>
@@ -802,9 +841,9 @@
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
-    <col width="27" customWidth="1" min="26" max="26"/>
+    <col width="32" customWidth="1" min="26" max="26"/>
     <col width="19" customWidth="1" min="27" max="27"/>
-    <col width="14" customWidth="1" min="28" max="28"/>
+    <col width="17" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
@@ -814,7 +853,7 @@
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="16" customWidth="1" min="38" max="38"/>
+    <col width="18" customWidth="1" min="38" max="38"/>
     <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
@@ -823,7 +862,7 @@
     <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
-    <col width="24" customWidth="1" min="47" max="47"/>
+    <col width="32" customWidth="1" min="47" max="47"/>
     <col width="45" customWidth="1" min="48" max="48"/>
     <col width="25" customWidth="1" min="49" max="49"/>
     <col width="23" customWidth="1" min="50" max="50"/>
@@ -1564,10 +1603,8 @@
           <t>Prabin Shrestha</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>9842739192</t>
-        </is>
+      <c r="O4" s="3" t="n">
+        <v>9842739192</v>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
@@ -1653,10 +1690,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN4" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN4" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO4" s="3" t="inlineStr">
         <is>
@@ -1667,35 +1702,247 @@
       <c r="AQ4" s="3" t="inlineStr"/>
       <c r="AR4" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT4" s="3" t="inlineStr">
+        <is>
+          <t>2d 1h 13m</t>
+        </is>
+      </c>
+      <c r="AU4" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV4" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS4" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT4" s="3" t="inlineStr">
-        <is>
-          <t>2d 1h 13m</t>
-        </is>
-      </c>
-      <c r="AU4" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV4" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
       <c r="AW4" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
       <c r="AX4" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 9:54 AM</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv isue  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>iptv isue</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>TKT1370375</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>Kiran shrestha</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>Kiran shrestha</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>9851057419</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>14 Oct 2026 01:27:11 PM</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="3" t="inlineStr"/>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t>9851057419</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t>14 Oct 2026 12:26:41 PM</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 09:54:52 AM</t>
+        </is>
+      </c>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y5" s="3" t="inlineStr">
+        <is>
+          <t>27.6741</t>
+        </is>
+      </c>
+      <c r="Z5" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA5" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC5" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD5" s="3" t="inlineStr"/>
+      <c r="AE5" s="3" t="inlineStr">
+        <is>
+          <t>"near Dibyashwari Party Palace,Madhyapur Thimi ", Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF5" s="3" t="inlineStr">
+        <is>
+          <t>godkiran20@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG5" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Remote damage Issue</t>
+        </is>
+      </c>
+      <c r="AH5" s="3" t="inlineStr"/>
+      <c r="AI5" s="3" t="inlineStr"/>
+      <c r="AJ5" s="3" t="inlineStr"/>
+      <c r="AK5" s="3" t="inlineStr"/>
+      <c r="AL5" s="3" t="inlineStr">
+        <is>
+          <t>Rejina Shrestha</t>
+        </is>
+      </c>
+      <c r="AM5" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN5" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO5" s="3" t="inlineStr">
+        <is>
+          <t>L9-3</t>
+        </is>
+      </c>
+      <c r="AP5" s="3" t="inlineStr">
+        <is>
+          <t>85.35918</t>
+        </is>
+      </c>
+      <c r="AQ5" s="3" t="inlineStr"/>
+      <c r="AR5" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv isue  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS5" s="3" t="inlineStr">
+        <is>
+          <t>20h 27m</t>
+        </is>
+      </c>
+      <c r="AT5" s="3" t="inlineStr">
+        <is>
+          <t>21h 28m</t>
+        </is>
+      </c>
+      <c r="AU5" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV5" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv isue  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW5" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX5" s="3" t="inlineStr">
         <is>
           <t>Shashikant Chaudhary</t>
         </is>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_15_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_15_Oct_2026.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -546,36 +546,54 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Shashikant Chaudhary</t>
+          <t>Sabin Giri</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n">
+      <c r="B5" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="C5" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="C4" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>75.0%</t>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -646,7 +664,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
     </row>
@@ -657,19 +675,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
     </row>
@@ -692,7 +710,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
     </row>
@@ -707,13 +725,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -729,10 +748,15 @@
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
@@ -748,9 +772,12 @@
         <v>1</v>
       </c>
       <c r="C2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D2" s="6" t="n">
+      <c r="E2" s="6" t="n">
         <v>2</v>
       </c>
     </row>
@@ -764,16 +791,19 @@
         <v>0</v>
       </c>
       <c r="C3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D3" s="6" t="n">
+      <c r="E3" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -782,24 +812,49 @@
       <c r="C4" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="D4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="C6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="D5" s="4" t="n">
-        <v>4</v>
+      <c r="E6" s="4" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -813,11 +868,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX5"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="35" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -853,7 +908,7 @@
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="18" customWidth="1" min="38" max="38"/>
+    <col width="19" customWidth="1" min="38" max="38"/>
     <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
@@ -1793,20 +1848,14 @@
           <t>On Hold</t>
         </is>
       </c>
-      <c r="M5" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M5" s="3" t="inlineStr"/>
       <c r="N5" s="3" t="inlineStr">
         <is>
           <t>Kiran shrestha</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>9851057419</t>
-        </is>
+      <c r="O5" s="3" t="n">
+        <v>9851057419</v>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
@@ -1896,47 +1945,43 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN5" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN5" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO5" s="3" t="inlineStr">
         <is>
           <t>L9-3</t>
         </is>
       </c>
-      <c r="AP5" s="3" t="inlineStr">
-        <is>
-          <t>85.35918</t>
-        </is>
+      <c r="AP5" s="3" t="n">
+        <v>85.35917999999999</v>
       </c>
       <c r="AQ5" s="3" t="inlineStr"/>
       <c r="AR5" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS5" s="3" t="inlineStr">
+        <is>
+          <t>20h 27m</t>
+        </is>
+      </c>
+      <c r="AT5" s="3" t="inlineStr">
+        <is>
+          <t>21h 28m</t>
+        </is>
+      </c>
+      <c r="AU5" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV5" s="3" t="inlineStr">
+        <is>
           <t>Case : iptv isue  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS5" s="3" t="inlineStr">
-        <is>
-          <t>20h 27m</t>
-        </is>
-      </c>
-      <c r="AT5" s="3" t="inlineStr">
-        <is>
-          <t>21h 28m</t>
-        </is>
-      </c>
-      <c r="AU5" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (On Hold)</t>
-        </is>
-      </c>
-      <c r="AV5" s="3" t="inlineStr">
-        <is>
-          <t>Case : iptv isue  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
       <c r="AW5" s="3" t="inlineStr">
         <is>
           <t>IPTV Issue</t>
@@ -1945,6 +1990,226 @@
       <c r="AX5" s="3" t="inlineStr">
         <is>
           <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 10:03 AM</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>IPTV ISSUE</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>TKT1371185</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>Tej Prasad Poudel</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>Tej Prasad Poudel</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>9749400360</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr"/>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 10:03:39 AM</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="inlineStr"/>
+      <c r="T6" s="3" t="inlineStr"/>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t>9851268100</t>
+        </is>
+      </c>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
+          <t>14 Oct 2026 08:09:16 PM</t>
+        </is>
+      </c>
+      <c r="W6" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 10:03:39 AM</t>
+        </is>
+      </c>
+      <c r="X6" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y6" s="3" t="inlineStr">
+        <is>
+          <t>27.73249</t>
+        </is>
+      </c>
+      <c r="Z6" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA6" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC6" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD6" s="3" t="inlineStr"/>
+      <c r="AE6" s="3" t="inlineStr">
+        <is>
+          <t>Near to Manakamana Futsal , Makalbari , Kathmandu, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF6" s="3" t="inlineStr">
+        <is>
+          <t>poudelp891@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG6" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH6" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI6" s="3" t="inlineStr">
+        <is>
+          <t>00:03 hour</t>
+        </is>
+      </c>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" s="3" t="inlineStr">
+        <is>
+          <t>Prajwal Adhikari</t>
+        </is>
+      </c>
+      <c r="AM6" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN6" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO6" s="3" t="inlineStr">
+        <is>
+          <t>L20-5</t>
+        </is>
+      </c>
+      <c r="AP6" s="3" t="inlineStr">
+        <is>
+          <t>85.3889</t>
+        </is>
+      </c>
+      <c r="AQ6" s="3" t="inlineStr"/>
+      <c r="AR6" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS6" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT6" s="3" t="inlineStr">
+        <is>
+          <t>13h 54m</t>
+        </is>
+      </c>
+      <c r="AU6" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV6" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW6" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX6" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_15_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_15_Oct_2026.xlsx
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>4</v>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
@@ -687,7 +687,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -710,7 +710,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -822,7 +822,7 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Other / Uncategorized</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -839,22 +839,41 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B7" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="4" t="n">
+      <c r="C7" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D6" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>5</v>
+      <c r="D7" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -868,7 +887,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX6"/>
+  <dimension ref="A1:AX7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -914,7 +933,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -2060,10 +2079,8 @@
           <t>Tej Prasad Poudel</t>
         </is>
       </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t>9749400360</t>
-        </is>
+      <c r="O6" s="3" t="n">
+        <v>9749400360</v>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
@@ -2139,10 +2156,8 @@
           <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
-      <c r="AH6" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH6" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI6" s="3" t="inlineStr">
         <is>
@@ -2161,47 +2176,43 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN6" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN6" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO6" s="3" t="inlineStr">
         <is>
           <t>L20-5</t>
         </is>
       </c>
-      <c r="AP6" s="3" t="inlineStr">
-        <is>
-          <t>85.3889</t>
-        </is>
+      <c r="AP6" s="3" t="n">
+        <v>85.38890000000001</v>
       </c>
       <c r="AQ6" s="3" t="inlineStr"/>
       <c r="AR6" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS6" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT6" s="3" t="inlineStr">
+        <is>
+          <t>13h 54m</t>
+        </is>
+      </c>
+      <c r="AU6" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV6" s="3" t="inlineStr">
+        <is>
           <t>Case : IPTV ISSUE   has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AS6" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT6" s="3" t="inlineStr">
-        <is>
-          <t>13h 54m</t>
-        </is>
-      </c>
-      <c r="AU6" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV6" s="3" t="inlineStr">
-        <is>
-          <t>Case : IPTV ISSUE   has been updated by Sabin Giri</t>
-        </is>
-      </c>
       <c r="AW6" s="3" t="inlineStr">
         <is>
           <t>IPTV Issue</t>
@@ -2210,6 +2221,114 @@
       <c r="AX6" s="3" t="inlineStr">
         <is>
           <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 10:19 AM</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI RANGE ISSUE  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr"/>
+      <c r="J7" s="3" t="inlineStr"/>
+      <c r="K7" s="3" t="inlineStr"/>
+      <c r="L7" s="3" t="inlineStr"/>
+      <c r="M7" s="3" t="inlineStr"/>
+      <c r="N7" s="3" t="inlineStr"/>
+      <c r="O7" s="3" t="inlineStr"/>
+      <c r="P7" s="3" t="inlineStr"/>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr"/>
+      <c r="S7" s="3" t="inlineStr"/>
+      <c r="T7" s="3" t="inlineStr"/>
+      <c r="U7" s="3" t="inlineStr"/>
+      <c r="V7" s="3" t="inlineStr"/>
+      <c r="W7" s="3" t="inlineStr"/>
+      <c r="X7" s="3" t="inlineStr"/>
+      <c r="Y7" s="3" t="inlineStr"/>
+      <c r="Z7" s="3" t="inlineStr"/>
+      <c r="AA7" s="3" t="inlineStr"/>
+      <c r="AB7" s="3" t="inlineStr"/>
+      <c r="AC7" s="3" t="inlineStr"/>
+      <c r="AD7" s="3" t="inlineStr"/>
+      <c r="AE7" s="3" t="inlineStr"/>
+      <c r="AF7" s="3" t="inlineStr"/>
+      <c r="AG7" s="3" t="inlineStr"/>
+      <c r="AH7" s="3" t="inlineStr"/>
+      <c r="AI7" s="3" t="inlineStr"/>
+      <c r="AJ7" s="3" t="inlineStr"/>
+      <c r="AK7" s="3" t="inlineStr"/>
+      <c r="AL7" s="3" t="inlineStr"/>
+      <c r="AM7" s="3" t="inlineStr"/>
+      <c r="AN7" s="3" t="inlineStr"/>
+      <c r="AO7" s="3" t="inlineStr"/>
+      <c r="AP7" s="3" t="inlineStr"/>
+      <c r="AQ7" s="3" t="inlineStr"/>
+      <c r="AR7" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS7" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT7" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU7" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV7" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI RANGE ISSUE  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW7" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX7" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_15_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_15_Oct_2026.xlsx
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>71.4%</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>14.3%</t>
         </is>
       </c>
     </row>
@@ -687,7 +687,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>28.6%</t>
         </is>
       </c>
     </row>
@@ -698,10 +698,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>42.9%</t>
         </is>
       </c>
     </row>
@@ -775,10 +775,10 @@
         <v>0</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -870,10 +870,10 @@
         <v>1</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -887,7 +887,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX7"/>
+  <dimension ref="A1:AX8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -933,7 +933,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -2332,6 +2332,222 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 10:56 AM</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>TKT1371415</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>Sagar Bhandari</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>Sagar Bhandari</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>9845216742</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr"/>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 10:56:38 AM</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr"/>
+      <c r="T8" s="3" t="inlineStr"/>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t>9845216742</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 09:07:41 AM</t>
+        </is>
+      </c>
+      <c r="W8" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 10:56:38 AM</t>
+        </is>
+      </c>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y8" s="3" t="inlineStr">
+        <is>
+          <t>27.68709</t>
+        </is>
+      </c>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA8" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB8" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC8" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD8" s="3" t="inlineStr"/>
+      <c r="AE8" s="3" t="inlineStr">
+        <is>
+          <t>Near North point mall - Shopping mall Bode Nyumola Marg Madhyapur Thimi 44600, Bagmati, Central, Nep</t>
+        </is>
+      </c>
+      <c r="AF8" s="3" t="inlineStr">
+        <is>
+          <t>yrts333@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG8" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH8" s="3" t="inlineStr"/>
+      <c r="AI8" s="3" t="inlineStr">
+        <is>
+          <t>00:56 hour</t>
+        </is>
+      </c>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM8" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN8" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO8" s="3" t="inlineStr">
+        <is>
+          <t>L20-7</t>
+        </is>
+      </c>
+      <c r="AP8" s="3" t="inlineStr">
+        <is>
+          <t>85.39133</t>
+        </is>
+      </c>
+      <c r="AQ8" s="3" t="inlineStr"/>
+      <c r="AR8" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS8" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT8" s="3" t="inlineStr">
+        <is>
+          <t>1h 48m</t>
+        </is>
+      </c>
+      <c r="AU8" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV8" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW8" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX8" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_15_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_15_Oct_2026.xlsx
@@ -933,7 +933,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -2399,10 +2399,8 @@
           <t>Sagar Bhandari</t>
         </is>
       </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t>9845216742</t>
-        </is>
+      <c r="O8" s="3" t="n">
+        <v>9845216742</v>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
@@ -2496,25 +2494,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN8" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN8" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO8" s="3" t="inlineStr">
         <is>
           <t>L20-7</t>
         </is>
       </c>
-      <c r="AP8" s="3" t="inlineStr">
-        <is>
-          <t>85.39133</t>
-        </is>
+      <c r="AP8" s="3" t="n">
+        <v>85.39133</v>
       </c>
       <c r="AQ8" s="3" t="inlineStr"/>
       <c r="AR8" s="3" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS8" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_15_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_15_Oct_2026.xlsx
@@ -532,10 +532,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="C5" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="C5" s="4" t="n">
-        <v>5</v>
-      </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>77.8%</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>11.1%</t>
         </is>
       </c>
     </row>
@@ -687,7 +687,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>22.2%</t>
         </is>
       </c>
     </row>
@@ -698,10 +698,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>55.6%</t>
         </is>
       </c>
     </row>
@@ -769,16 +769,16 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -864,16 +864,16 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -887,7 +887,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX8"/>
+  <dimension ref="A1:AX10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -900,10 +900,10 @@
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="21" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -921,7 +921,7 @@
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
-    <col width="23" customWidth="1" min="32" max="32"/>
+    <col width="25" customWidth="1" min="32" max="32"/>
     <col width="29" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
@@ -933,7 +933,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -2542,6 +2542,430 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 11:39 AM</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>TKT1369445</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>Madhu Sudhan Kadel</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>Madhu Sudhan Kadel</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>9841731253</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="inlineStr"/>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 11:39:57 AM</t>
+        </is>
+      </c>
+      <c r="S9" s="3" t="inlineStr"/>
+      <c r="T9" s="3" t="inlineStr"/>
+      <c r="U9" s="3" t="inlineStr">
+        <is>
+          <t>9841339805</t>
+        </is>
+      </c>
+      <c r="V9" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 04:59:01 PM</t>
+        </is>
+      </c>
+      <c r="W9" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 11:39:57 AM</t>
+        </is>
+      </c>
+      <c r="X9" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y9" s="3" t="inlineStr">
+        <is>
+          <t>27.673072</t>
+        </is>
+      </c>
+      <c r="Z9" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA9" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB9" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC9" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD9" s="3" t="inlineStr"/>
+      <c r="AE9" s="3" t="inlineStr">
+        <is>
+          <t>Near Purnachandimarg M8F9+6FQ, Lalitpur 44600 - Lalitpur Metropolitan, Lalitpur, Bagmati, Central, N</t>
+        </is>
+      </c>
+      <c r="AF9" s="3" t="inlineStr">
+        <is>
+          <t>lovelyjshahi@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG9" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH9" s="3" t="inlineStr"/>
+      <c r="AI9" s="3" t="inlineStr">
+        <is>
+          <t>14:40 hour</t>
+        </is>
+      </c>
+      <c r="AJ9" s="3" t="inlineStr"/>
+      <c r="AK9" s="3" t="inlineStr"/>
+      <c r="AL9" s="3" t="inlineStr">
+        <is>
+          <t>Nirajan Dhamala</t>
+        </is>
+      </c>
+      <c r="AM9" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN9" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO9" s="3" t="inlineStr">
+        <is>
+          <t>1,11</t>
+        </is>
+      </c>
+      <c r="AP9" s="3" t="inlineStr">
+        <is>
+          <t>85.319737</t>
+        </is>
+      </c>
+      <c r="AQ9" s="3" t="inlineStr"/>
+      <c r="AR9" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS9" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT9" s="3" t="inlineStr">
+        <is>
+          <t>1d 18h 40m</t>
+        </is>
+      </c>
+      <c r="AU9" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV9" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW9" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX9" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 11:42 AM</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>TKT1370833</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>Janak Bahadur Shahi</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>Janak Bahadur Shahi</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>9767528111</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="inlineStr"/>
+      <c r="R10" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 11:42:15 AM</t>
+        </is>
+      </c>
+      <c r="S10" s="3" t="inlineStr"/>
+      <c r="T10" s="3" t="inlineStr"/>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t>9767528111</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t>14 Oct 2026 04:17:04 PM</t>
+        </is>
+      </c>
+      <c r="W10" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 11:42:15 AM</t>
+        </is>
+      </c>
+      <c r="X10" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y10" s="3" t="inlineStr"/>
+      <c r="Z10" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA10" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB10" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC10" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD10" s="3" t="inlineStr"/>
+      <c r="AE10" s="3" t="inlineStr">
+        <is>
+          <t>Aloknagar Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF10" s="3" t="inlineStr"/>
+      <c r="AG10" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH10" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI10" s="3" t="inlineStr">
+        <is>
+          <t>05:25 hour</t>
+        </is>
+      </c>
+      <c r="AJ10" s="3" t="inlineStr"/>
+      <c r="AK10" s="3" t="inlineStr"/>
+      <c r="AL10" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM10" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN10" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO10" s="3" t="inlineStr">
+        <is>
+          <t>2,5</t>
+        </is>
+      </c>
+      <c r="AP10" s="3" t="inlineStr"/>
+      <c r="AQ10" s="3" t="inlineStr"/>
+      <c r="AR10" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS10" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT10" s="3" t="inlineStr">
+        <is>
+          <t>19h 25m</t>
+        </is>
+      </c>
+      <c r="AU10" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV10" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW10" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX10" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_15_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_15_Oct_2026.xlsx
@@ -933,7 +933,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -2609,10 +2609,8 @@
           <t>Madhu Sudhan Kadel</t>
         </is>
       </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>9841731253</t>
-        </is>
+      <c r="O9" s="3" t="n">
+        <v>9841731253</v>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
@@ -2706,25 +2704,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN9" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN9" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO9" s="3" t="inlineStr">
         <is>
           <t>1,11</t>
         </is>
       </c>
-      <c r="AP9" s="3" t="inlineStr">
-        <is>
-          <t>85.319737</t>
-        </is>
+      <c r="AP9" s="3" t="n">
+        <v>85.319737</v>
       </c>
       <c r="AQ9" s="3" t="inlineStr"/>
       <c r="AR9" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6   has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS9" s="3" t="inlineStr">
@@ -2825,10 +2819,8 @@
           <t>Janak Bahadur Shahi</t>
         </is>
       </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t>9767528111</t>
-        </is>
+      <c r="O10" s="3" t="n">
+        <v>9767528111</v>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
@@ -2896,10 +2888,8 @@
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="AH10" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH10" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI10" s="3" t="inlineStr">
         <is>
@@ -2918,10 +2908,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN10" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN10" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO10" s="3" t="inlineStr">
         <is>
@@ -2932,7 +2920,7 @@
       <c r="AQ10" s="3" t="inlineStr"/>
       <c r="AR10" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS10" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_15_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_15_Oct_2026.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -564,36 +564,54 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Shashikant Chaudhary</t>
+          <t>Sanjeev Giri</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="C5" s="4" t="n">
+      <c r="B6" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C6" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>77.8%</t>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>70.0%</t>
         </is>
       </c>
     </row>
@@ -664,7 +682,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>10.0%</t>
         </is>
       </c>
     </row>
@@ -687,7 +705,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>20.0%</t>
         </is>
       </c>
     </row>
@@ -710,7 +728,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -887,7 +905,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX10"/>
+  <dimension ref="A1:AX11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -2954,6 +2972,114 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 12:13 PM</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Case : Gaming issue   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr"/>
+      <c r="J11" s="3" t="inlineStr"/>
+      <c r="K11" s="3" t="inlineStr"/>
+      <c r="L11" s="3" t="inlineStr"/>
+      <c r="M11" s="3" t="inlineStr"/>
+      <c r="N11" s="3" t="inlineStr"/>
+      <c r="O11" s="3" t="inlineStr"/>
+      <c r="P11" s="3" t="inlineStr"/>
+      <c r="Q11" s="3" t="inlineStr"/>
+      <c r="R11" s="3" t="inlineStr"/>
+      <c r="S11" s="3" t="inlineStr"/>
+      <c r="T11" s="3" t="inlineStr"/>
+      <c r="U11" s="3" t="inlineStr"/>
+      <c r="V11" s="3" t="inlineStr"/>
+      <c r="W11" s="3" t="inlineStr"/>
+      <c r="X11" s="3" t="inlineStr"/>
+      <c r="Y11" s="3" t="inlineStr"/>
+      <c r="Z11" s="3" t="inlineStr"/>
+      <c r="AA11" s="3" t="inlineStr"/>
+      <c r="AB11" s="3" t="inlineStr"/>
+      <c r="AC11" s="3" t="inlineStr"/>
+      <c r="AD11" s="3" t="inlineStr"/>
+      <c r="AE11" s="3" t="inlineStr"/>
+      <c r="AF11" s="3" t="inlineStr"/>
+      <c r="AG11" s="3" t="inlineStr"/>
+      <c r="AH11" s="3" t="inlineStr"/>
+      <c r="AI11" s="3" t="inlineStr"/>
+      <c r="AJ11" s="3" t="inlineStr"/>
+      <c r="AK11" s="3" t="inlineStr"/>
+      <c r="AL11" s="3" t="inlineStr"/>
+      <c r="AM11" s="3" t="inlineStr"/>
+      <c r="AN11" s="3" t="inlineStr"/>
+      <c r="AO11" s="3" t="inlineStr"/>
+      <c r="AP11" s="3" t="inlineStr"/>
+      <c r="AQ11" s="3" t="inlineStr"/>
+      <c r="AR11" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS11" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT11" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU11" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV11" s="3" t="inlineStr">
+        <is>
+          <t>Case : Gaming issue   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW11" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX11" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_15_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_15_Oct_2026.xlsx
@@ -568,7 +568,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>0</v>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>7</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>63.6%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>9.1%</t>
         </is>
       </c>
     </row>
@@ -705,7 +705,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>18.2%</t>
         </is>
       </c>
     </row>
@@ -728,7 +728,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>45.5%</t>
         </is>
       </c>
     </row>
@@ -905,7 +905,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX11"/>
+  <dimension ref="A1:AX12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -3080,6 +3080,114 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 1:11 PM</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr"/>
+      <c r="J12" s="3" t="inlineStr"/>
+      <c r="K12" s="3" t="inlineStr"/>
+      <c r="L12" s="3" t="inlineStr"/>
+      <c r="M12" s="3" t="inlineStr"/>
+      <c r="N12" s="3" t="inlineStr"/>
+      <c r="O12" s="3" t="inlineStr"/>
+      <c r="P12" s="3" t="inlineStr"/>
+      <c r="Q12" s="3" t="inlineStr"/>
+      <c r="R12" s="3" t="inlineStr"/>
+      <c r="S12" s="3" t="inlineStr"/>
+      <c r="T12" s="3" t="inlineStr"/>
+      <c r="U12" s="3" t="inlineStr"/>
+      <c r="V12" s="3" t="inlineStr"/>
+      <c r="W12" s="3" t="inlineStr"/>
+      <c r="X12" s="3" t="inlineStr"/>
+      <c r="Y12" s="3" t="inlineStr"/>
+      <c r="Z12" s="3" t="inlineStr"/>
+      <c r="AA12" s="3" t="inlineStr"/>
+      <c r="AB12" s="3" t="inlineStr"/>
+      <c r="AC12" s="3" t="inlineStr"/>
+      <c r="AD12" s="3" t="inlineStr"/>
+      <c r="AE12" s="3" t="inlineStr"/>
+      <c r="AF12" s="3" t="inlineStr"/>
+      <c r="AG12" s="3" t="inlineStr"/>
+      <c r="AH12" s="3" t="inlineStr"/>
+      <c r="AI12" s="3" t="inlineStr"/>
+      <c r="AJ12" s="3" t="inlineStr"/>
+      <c r="AK12" s="3" t="inlineStr"/>
+      <c r="AL12" s="3" t="inlineStr"/>
+      <c r="AM12" s="3" t="inlineStr"/>
+      <c r="AN12" s="3" t="inlineStr"/>
+      <c r="AO12" s="3" t="inlineStr"/>
+      <c r="AP12" s="3" t="inlineStr"/>
+      <c r="AQ12" s="3" t="inlineStr"/>
+      <c r="AR12" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS12" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT12" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU12" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV12" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW12" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX12" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_15_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_15_Oct_2026.xlsx
@@ -532,10 +532,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>8.3%</t>
         </is>
       </c>
     </row>
@@ -705,7 +705,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
@@ -716,10 +716,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>0</v>
@@ -796,7 +796,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>1</v>
@@ -891,7 +891,7 @@
         <v>6</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -905,7 +905,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX12"/>
+  <dimension ref="A1:AX13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -918,10 +918,10 @@
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="31" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="31" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -951,7 +951,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -3188,6 +3188,222 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 1:29 PM</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>TKT1370651</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>Afjal Turbo Repairing Center</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>Afjal Turbo Repairing Center</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t>9808397799</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q13" s="3" t="inlineStr"/>
+      <c r="R13" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 01:29:17 PM</t>
+        </is>
+      </c>
+      <c r="S13" s="3" t="inlineStr"/>
+      <c r="T13" s="3" t="inlineStr"/>
+      <c r="U13" s="3" t="inlineStr">
+        <is>
+          <t>9808397799</t>
+        </is>
+      </c>
+      <c r="V13" s="3" t="inlineStr">
+        <is>
+          <t>14 Oct 2026 02:56:25 PM</t>
+        </is>
+      </c>
+      <c r="W13" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 01:29:17 PM</t>
+        </is>
+      </c>
+      <c r="X13" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y13" s="3" t="inlineStr">
+        <is>
+          <t>27.684346</t>
+        </is>
+      </c>
+      <c r="Z13" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA13" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB13" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC13" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD13" s="3" t="inlineStr"/>
+      <c r="AE13" s="3" t="inlineStr">
+        <is>
+          <t>Sanepa-2, Lalitpur, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF13" s="3" t="inlineStr">
+        <is>
+          <t>afjalturbo9@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG13" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH13" s="3" t="inlineStr"/>
+      <c r="AI13" s="3" t="inlineStr">
+        <is>
+          <t>08:33 hour</t>
+        </is>
+      </c>
+      <c r="AJ13" s="3" t="inlineStr"/>
+      <c r="AK13" s="3" t="inlineStr"/>
+      <c r="AL13" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM13" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN13" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO13" s="3" t="inlineStr">
+        <is>
+          <t>1,12</t>
+        </is>
+      </c>
+      <c r="AP13" s="3" t="inlineStr">
+        <is>
+          <t>85.300288</t>
+        </is>
+      </c>
+      <c r="AQ13" s="3" t="inlineStr"/>
+      <c r="AR13" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS13" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT13" s="3" t="inlineStr">
+        <is>
+          <t>22h 32m</t>
+        </is>
+      </c>
+      <c r="AU13" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV13" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW13" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX13" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_15_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_15_Oct_2026.xlsx
@@ -951,7 +951,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -3255,10 +3255,8 @@
           <t>Afjal Turbo Repairing Center</t>
         </is>
       </c>
-      <c r="O13" s="3" t="inlineStr">
-        <is>
-          <t>9808397799</t>
-        </is>
+      <c r="O13" s="3" t="n">
+        <v>9808397799</v>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
@@ -3352,25 +3350,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN13" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN13" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO13" s="3" t="inlineStr">
         <is>
           <t>1,12</t>
         </is>
       </c>
-      <c r="AP13" s="3" t="inlineStr">
-        <is>
-          <t>85.300288</t>
-        </is>
+      <c r="AP13" s="3" t="n">
+        <v>85.30028799999999</v>
       </c>
       <c r="AQ13" s="3" t="inlineStr"/>
       <c r="AR13" s="3" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS13" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_15_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_15_Oct_2026.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -586,32 +586,50 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>71.4%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>66.7%</t>
+      <c r="B7" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>78.9%</t>
         </is>
       </c>
     </row>
@@ -670,10 +688,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
@@ -682,7 +700,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>21.1%</t>
         </is>
       </c>
     </row>
@@ -705,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>10.5%</t>
         </is>
       </c>
     </row>
@@ -716,10 +734,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
@@ -728,7 +746,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>52.6%</t>
         </is>
       </c>
     </row>
@@ -743,14 +761,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="29" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -776,6 +795,11 @@
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
           <t>Grand Total</t>
         </is>
       </c>
@@ -793,10 +817,13 @@
         <v>0</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E2" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" s="6" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -814,52 +841,61 @@
       <c r="D3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E3" s="6" t="n">
+      <c r="E3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Configuration Issue</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="E4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Other / Uncategorized</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D5" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" s="6" t="n">
+      <c r="E5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Other / Uncategorized</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
@@ -871,27 +907,77 @@
       <c r="D6" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="E6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="B9" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="C7" s="4" t="n">
+      <c r="C9" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D7" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>10</v>
+      <c r="D9" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -905,7 +991,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX13"/>
+  <dimension ref="A1:AX20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -916,7 +1002,7 @@
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="31" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
@@ -940,7 +1026,7 @@
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
     <col width="25" customWidth="1" min="32" max="32"/>
-    <col width="29" customWidth="1" min="33" max="33"/>
+    <col width="30" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
@@ -951,7 +1037,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -3398,6 +3484,1510 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 1:53 PM</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>TKT1371449</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>Sushan Shrestha</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>Sushan Shrestha</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t>9851174382</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q14" s="3" t="inlineStr"/>
+      <c r="R14" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 01:53:33 PM</t>
+        </is>
+      </c>
+      <c r="S14" s="3" t="inlineStr"/>
+      <c r="T14" s="3" t="inlineStr"/>
+      <c r="U14" s="3" t="inlineStr">
+        <is>
+          <t>9851174382</t>
+        </is>
+      </c>
+      <c r="V14" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 09:41:16 AM</t>
+        </is>
+      </c>
+      <c r="W14" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 01:53:33 PM</t>
+        </is>
+      </c>
+      <c r="X14" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y14" s="3" t="inlineStr">
+        <is>
+          <t>27.66926</t>
+        </is>
+      </c>
+      <c r="Z14" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA14" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB14" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC14" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD14" s="3" t="inlineStr"/>
+      <c r="AE14" s="3" t="inlineStr">
+        <is>
+          <t>Bhaktapur Lokanthali ward no:1 near creation driving center and mutton station, Bagmati, Central, Ne</t>
+        </is>
+      </c>
+      <c r="AF14" s="3" t="inlineStr">
+        <is>
+          <t>sushanstha25@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG14" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH14" s="3" t="inlineStr"/>
+      <c r="AI14" s="3" t="inlineStr">
+        <is>
+          <t>03:53 hour</t>
+        </is>
+      </c>
+      <c r="AJ14" s="3" t="inlineStr"/>
+      <c r="AK14" s="3" t="inlineStr"/>
+      <c r="AL14" s="3" t="inlineStr">
+        <is>
+          <t>Bipana Neupane</t>
+        </is>
+      </c>
+      <c r="AM14" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN14" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO14" s="3" t="inlineStr">
+        <is>
+          <t>3,5</t>
+        </is>
+      </c>
+      <c r="AP14" s="3" t="inlineStr">
+        <is>
+          <t>85.35306</t>
+        </is>
+      </c>
+      <c r="AQ14" s="3" t="inlineStr"/>
+      <c r="AR14" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS14" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT14" s="3" t="inlineStr">
+        <is>
+          <t>4h 12m</t>
+        </is>
+      </c>
+      <c r="AU14" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV14" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW14" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX14" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 1:58 PM</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr"/>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router faulty   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>Router faulty</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>TKT1371466</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>Mgc associates  pvt ltd</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>Mgc associates  pvt ltd</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t>9815239074</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q15" s="3" t="inlineStr"/>
+      <c r="R15" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 10:06:14 AM</t>
+        </is>
+      </c>
+      <c r="S15" s="3" t="inlineStr"/>
+      <c r="T15" s="3" t="inlineStr"/>
+      <c r="U15" s="3" t="inlineStr">
+        <is>
+          <t>KLK9815239074</t>
+        </is>
+      </c>
+      <c r="V15" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 09:56:39 AM</t>
+        </is>
+      </c>
+      <c r="W15" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 01:58:47 PM</t>
+        </is>
+      </c>
+      <c r="X15" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y15" s="3" t="inlineStr"/>
+      <c r="Z15" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA15" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB15" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC15" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD15" s="3" t="inlineStr"/>
+      <c r="AE15" s="3" t="inlineStr">
+        <is>
+          <t>Chamati Dabu - Cultural landmark P78X+QJ4 15 Ropeway Sadak Kathmandu 44600, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF15" s="3" t="inlineStr">
+        <is>
+          <t>9815239074@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG15" s="3" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="AH15" s="3" t="inlineStr"/>
+      <c r="AI15" s="3" t="inlineStr">
+        <is>
+          <t>03:58 hour</t>
+        </is>
+      </c>
+      <c r="AJ15" s="3" t="inlineStr"/>
+      <c r="AK15" s="3" t="inlineStr"/>
+      <c r="AL15" s="3" t="inlineStr">
+        <is>
+          <t>Bhawana Bista</t>
+        </is>
+      </c>
+      <c r="AM15" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN15" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO15" s="3" t="inlineStr">
+        <is>
+          <t>CDB213</t>
+        </is>
+      </c>
+      <c r="AP15" s="3" t="inlineStr"/>
+      <c r="AQ15" s="3" t="inlineStr"/>
+      <c r="AR15" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router faulty   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS15" s="3" t="inlineStr">
+        <is>
+          <t>3h 52m</t>
+        </is>
+      </c>
+      <c r="AT15" s="3" t="inlineStr">
+        <is>
+          <t>4h 2m</t>
+        </is>
+      </c>
+      <c r="AU15" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV15" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router faulty   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW15" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX15" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 1:57 PM</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr"/>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>Case : 5g name not showing   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>5g name not showing</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>TKT1370413</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>Biraz Lama</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>Biraz Lama</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>9703511099</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q16" s="3" t="inlineStr"/>
+      <c r="R16" s="3" t="inlineStr">
+        <is>
+          <t>14 Oct 2026 05:45:44 PM</t>
+        </is>
+      </c>
+      <c r="S16" s="3" t="inlineStr"/>
+      <c r="T16" s="3" t="inlineStr"/>
+      <c r="U16" s="3" t="inlineStr">
+        <is>
+          <t>KLK9703511099</t>
+        </is>
+      </c>
+      <c r="V16" s="3" t="inlineStr">
+        <is>
+          <t>14 Oct 2026 12:53:25 PM</t>
+        </is>
+      </c>
+      <c r="W16" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 01:57:25 PM</t>
+        </is>
+      </c>
+      <c r="X16" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y16" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z16" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA16" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB16" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC16" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD16" s="3" t="inlineStr"/>
+      <c r="AE16" s="3" t="inlineStr">
+        <is>
+          <t>Chaumati, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF16" s="3" t="inlineStr">
+        <is>
+          <t>9703511099@g.com</t>
+        </is>
+      </c>
+      <c r="AG16" s="3" t="inlineStr">
+        <is>
+          <t>Configuration Issue</t>
+        </is>
+      </c>
+      <c r="AH16" s="3" t="inlineStr"/>
+      <c r="AI16" s="3" t="inlineStr">
+        <is>
+          <t>11:03 hour</t>
+        </is>
+      </c>
+      <c r="AJ16" s="3" t="inlineStr"/>
+      <c r="AK16" s="3" t="inlineStr"/>
+      <c r="AL16" s="3" t="inlineStr">
+        <is>
+          <t>Nirmaya Mukhiya</t>
+        </is>
+      </c>
+      <c r="AM16" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN16" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO16" s="3" t="inlineStr">
+        <is>
+          <t>CDB401</t>
+        </is>
+      </c>
+      <c r="AP16" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ16" s="3" t="inlineStr"/>
+      <c r="AR16" s="3" t="inlineStr">
+        <is>
+          <t>Case : 5g name not showing   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS16" s="3" t="inlineStr">
+        <is>
+          <t>20h 11m</t>
+        </is>
+      </c>
+      <c r="AT16" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 4m</t>
+        </is>
+      </c>
+      <c r="AU16" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV16" s="3" t="inlineStr">
+        <is>
+          <t>Case : 5g name not showing   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW16" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX16" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 1:56 PM</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr"/>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Case : 5g name not showing   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>5g name not showing</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>TKT1370413</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>Biraz Lama</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>Biraz Lama</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>9703511099</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q17" s="3" t="inlineStr"/>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t>14 Oct 2026 05:45:44 PM</t>
+        </is>
+      </c>
+      <c r="S17" s="3" t="inlineStr"/>
+      <c r="T17" s="3" t="inlineStr"/>
+      <c r="U17" s="3" t="inlineStr">
+        <is>
+          <t>KLK9703511099</t>
+        </is>
+      </c>
+      <c r="V17" s="3" t="inlineStr">
+        <is>
+          <t>14 Oct 2026 12:53:25 PM</t>
+        </is>
+      </c>
+      <c r="W17" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 01:57:25 PM</t>
+        </is>
+      </c>
+      <c r="X17" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y17" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z17" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA17" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB17" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC17" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD17" s="3" t="inlineStr"/>
+      <c r="AE17" s="3" t="inlineStr">
+        <is>
+          <t>Chaumati, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF17" s="3" t="inlineStr">
+        <is>
+          <t>9703511099@g.com</t>
+        </is>
+      </c>
+      <c r="AG17" s="3" t="inlineStr">
+        <is>
+          <t>Configuration Issue</t>
+        </is>
+      </c>
+      <c r="AH17" s="3" t="inlineStr"/>
+      <c r="AI17" s="3" t="inlineStr">
+        <is>
+          <t>11:03 hour</t>
+        </is>
+      </c>
+      <c r="AJ17" s="3" t="inlineStr"/>
+      <c r="AK17" s="3" t="inlineStr"/>
+      <c r="AL17" s="3" t="inlineStr">
+        <is>
+          <t>Nirmaya Mukhiya</t>
+        </is>
+      </c>
+      <c r="AM17" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN17" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO17" s="3" t="inlineStr">
+        <is>
+          <t>CDB401</t>
+        </is>
+      </c>
+      <c r="AP17" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ17" s="3" t="inlineStr"/>
+      <c r="AR17" s="3" t="inlineStr">
+        <is>
+          <t>Case : 5g name not showing   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS17" s="3" t="inlineStr">
+        <is>
+          <t>20h 11m</t>
+        </is>
+      </c>
+      <c r="AT17" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 4m</t>
+        </is>
+      </c>
+      <c r="AU17" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV17" s="3" t="inlineStr">
+        <is>
+          <t>Case : 5g name not showing   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW17" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX17" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 1:55 PM</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr"/>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>TKT1370924</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>Sangita Shrestha</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>Sangita Shrestha</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t>9841525749</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="inlineStr"/>
+      <c r="R18" s="3" t="inlineStr">
+        <is>
+          <t>14 Oct 2026 04:51:50 PM</t>
+        </is>
+      </c>
+      <c r="S18" s="3" t="inlineStr"/>
+      <c r="T18" s="3" t="inlineStr"/>
+      <c r="U18" s="3" t="inlineStr">
+        <is>
+          <t>9841525749</t>
+        </is>
+      </c>
+      <c r="V18" s="3" t="inlineStr">
+        <is>
+          <t>14 Oct 2026 04:51:50 PM</t>
+        </is>
+      </c>
+      <c r="W18" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 01:55:16 PM</t>
+        </is>
+      </c>
+      <c r="X18" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y18" s="3" t="inlineStr">
+        <is>
+          <t>27.69669</t>
+        </is>
+      </c>
+      <c r="Z18" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA18" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB18" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC18" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD18" s="3" t="inlineStr"/>
+      <c r="AE18" s="3" t="inlineStr">
+        <is>
+          <t>Ravi Bhawan, ??????? ???, Kathmandu 44600 Near By Santoshi Mata Temple, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF18" s="3" t="inlineStr">
+        <is>
+          <t>work@cgnet.com.np</t>
+        </is>
+      </c>
+      <c r="AG18" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH18" s="3" t="inlineStr"/>
+      <c r="AI18" s="3" t="inlineStr">
+        <is>
+          <t>07:03 hour</t>
+        </is>
+      </c>
+      <c r="AJ18" s="3" t="inlineStr"/>
+      <c r="AK18" s="3" t="inlineStr"/>
+      <c r="AL18" s="3" t="inlineStr">
+        <is>
+          <t>Joshna Shrestha</t>
+        </is>
+      </c>
+      <c r="AM18" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN18" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO18" s="3" t="inlineStr">
+        <is>
+          <t>3,6</t>
+        </is>
+      </c>
+      <c r="AP18" s="3" t="inlineStr">
+        <is>
+          <t>85.2875</t>
+        </is>
+      </c>
+      <c r="AQ18" s="3" t="inlineStr"/>
+      <c r="AR18" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS18" s="3" t="inlineStr">
+        <is>
+          <t>21h 3m</t>
+        </is>
+      </c>
+      <c r="AT18" s="3" t="inlineStr">
+        <is>
+          <t>21h 3m</t>
+        </is>
+      </c>
+      <c r="AU18" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV18" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW18" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX18" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 1:54 PM</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>TKT1370924</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>Sangita Shrestha</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>Sangita Shrestha</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t>9841525749</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q19" s="3" t="inlineStr"/>
+      <c r="R19" s="3" t="inlineStr">
+        <is>
+          <t>14 Oct 2026 04:51:50 PM</t>
+        </is>
+      </c>
+      <c r="S19" s="3" t="inlineStr"/>
+      <c r="T19" s="3" t="inlineStr"/>
+      <c r="U19" s="3" t="inlineStr">
+        <is>
+          <t>9841525749</t>
+        </is>
+      </c>
+      <c r="V19" s="3" t="inlineStr">
+        <is>
+          <t>14 Oct 2026 04:51:50 PM</t>
+        </is>
+      </c>
+      <c r="W19" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 01:55:16 PM</t>
+        </is>
+      </c>
+      <c r="X19" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y19" s="3" t="inlineStr">
+        <is>
+          <t>27.69669</t>
+        </is>
+      </c>
+      <c r="Z19" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA19" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB19" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC19" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD19" s="3" t="inlineStr"/>
+      <c r="AE19" s="3" t="inlineStr">
+        <is>
+          <t>Ravi Bhawan, ??????? ???, Kathmandu 44600 Near By Santoshi Mata Temple, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF19" s="3" t="inlineStr">
+        <is>
+          <t>work@cgnet.com.np</t>
+        </is>
+      </c>
+      <c r="AG19" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH19" s="3" t="inlineStr"/>
+      <c r="AI19" s="3" t="inlineStr">
+        <is>
+          <t>07:03 hour</t>
+        </is>
+      </c>
+      <c r="AJ19" s="3" t="inlineStr"/>
+      <c r="AK19" s="3" t="inlineStr"/>
+      <c r="AL19" s="3" t="inlineStr">
+        <is>
+          <t>Joshna Shrestha</t>
+        </is>
+      </c>
+      <c r="AM19" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN19" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO19" s="3" t="inlineStr">
+        <is>
+          <t>3,6</t>
+        </is>
+      </c>
+      <c r="AP19" s="3" t="inlineStr">
+        <is>
+          <t>85.2875</t>
+        </is>
+      </c>
+      <c r="AQ19" s="3" t="inlineStr"/>
+      <c r="AR19" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS19" s="3" t="inlineStr">
+        <is>
+          <t>21h 3m</t>
+        </is>
+      </c>
+      <c r="AT19" s="3" t="inlineStr">
+        <is>
+          <t>21h 3m</t>
+        </is>
+      </c>
+      <c r="AU19" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV19" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW19" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX19" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 1:53 PM</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>TKT1370259</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>Shyam Shrestha</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>Shyam Shrestha</t>
+        </is>
+      </c>
+      <c r="O20" s="3" t="inlineStr">
+        <is>
+          <t>9860959933</t>
+        </is>
+      </c>
+      <c r="P20" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q20" s="3" t="inlineStr"/>
+      <c r="R20" s="3" t="inlineStr">
+        <is>
+          <t>14 Oct 2026 11:25:48 AM</t>
+        </is>
+      </c>
+      <c r="S20" s="3" t="inlineStr"/>
+      <c r="T20" s="3" t="inlineStr"/>
+      <c r="U20" s="3" t="inlineStr">
+        <is>
+          <t>9860959933</t>
+        </is>
+      </c>
+      <c r="V20" s="3" t="inlineStr">
+        <is>
+          <t>14 Oct 2026 11:25:48 AM</t>
+        </is>
+      </c>
+      <c r="W20" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 01:53:59 PM</t>
+        </is>
+      </c>
+      <c r="X20" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y20" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z20" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA20" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB20" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC20" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD20" s="3" t="inlineStr"/>
+      <c r="AE20" s="3" t="inlineStr">
+        <is>
+          <t>, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF20" s="3" t="inlineStr">
+        <is>
+          <t>cresthaboy2@gamil.com</t>
+        </is>
+      </c>
+      <c r="AG20" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH20" s="3" t="inlineStr"/>
+      <c r="AI20" s="3" t="inlineStr">
+        <is>
+          <t>12:28 hour</t>
+        </is>
+      </c>
+      <c r="AJ20" s="3" t="inlineStr"/>
+      <c r="AK20" s="3" t="inlineStr"/>
+      <c r="AL20" s="3" t="inlineStr">
+        <is>
+          <t>Monika Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM20" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN20" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO20" s="3" t="inlineStr">
+        <is>
+          <t>CDB196</t>
+        </is>
+      </c>
+      <c r="AP20" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ20" s="3" t="inlineStr"/>
+      <c r="AR20" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS20" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 28m</t>
+        </is>
+      </c>
+      <c r="AT20" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 28m</t>
+        </is>
+      </c>
+      <c r="AU20" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV20" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW20" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX20" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_15_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_15_Oct_2026.xlsx
@@ -532,10 +532,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
@@ -604,10 +604,10 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>78.9%</t>
+          <t>81.0%</t>
         </is>
       </c>
     </row>
@@ -688,10 +688,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
@@ -700,7 +700,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>28.6%</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>9.5%</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>47.6%</t>
         </is>
       </c>
     </row>
@@ -811,7 +811,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>0</v>
@@ -823,29 +823,29 @@
         <v>2</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>IPTV Remote damage Issue</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="E3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E3" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="F3" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -873,17 +873,17 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>IPTV Remote damage Issue</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>0</v>
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>1</v>
@@ -974,10 +974,10 @@
         <v>7</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -991,7 +991,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX20"/>
+  <dimension ref="A1:AX22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -3551,10 +3551,8 @@
           <t>Sushan Shrestha</t>
         </is>
       </c>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
-          <t>9851174382</t>
-        </is>
+      <c r="O14" s="3" t="n">
+        <v>9851174382</v>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
@@ -3648,25 +3646,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN14" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN14" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO14" s="3" t="inlineStr">
         <is>
           <t>3,5</t>
         </is>
       </c>
-      <c r="AP14" s="3" t="inlineStr">
-        <is>
-          <t>85.35306</t>
-        </is>
+      <c r="AP14" s="3" t="n">
+        <v>85.35306</v>
       </c>
       <c r="AQ14" s="3" t="inlineStr"/>
       <c r="AR14" s="3" t="inlineStr">
         <is>
-          <t>Case : WiFi 6   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS14" s="3" t="inlineStr">
@@ -3767,10 +3761,8 @@
           <t>Mgc associates  pvt ltd</t>
         </is>
       </c>
-      <c r="O15" s="3" t="inlineStr">
-        <is>
-          <t>9815239074</t>
-        </is>
+      <c r="O15" s="3" t="n">
+        <v>9815239074</v>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
@@ -3860,10 +3852,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN15" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN15" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO15" s="3" t="inlineStr">
         <is>
@@ -3874,7 +3864,7 @@
       <c r="AQ15" s="3" t="inlineStr"/>
       <c r="AR15" s="3" t="inlineStr">
         <is>
-          <t>Case : Router faulty   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS15" s="3" t="inlineStr">
@@ -3975,10 +3965,8 @@
           <t>Biraz Lama</t>
         </is>
       </c>
-      <c r="O16" s="3" t="inlineStr">
-        <is>
-          <t>9703511099</t>
-        </is>
+      <c r="O16" s="3" t="n">
+        <v>9703511099</v>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
@@ -4072,25 +4060,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN16" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN16" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO16" s="3" t="inlineStr">
         <is>
           <t>CDB401</t>
         </is>
       </c>
-      <c r="AP16" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP16" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ16" s="3" t="inlineStr"/>
       <c r="AR16" s="3" t="inlineStr">
         <is>
-          <t>Case : 5g name not showing   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS16" s="3" t="inlineStr">
@@ -4191,10 +4175,8 @@
           <t>Biraz Lama</t>
         </is>
       </c>
-      <c r="O17" s="3" t="inlineStr">
-        <is>
-          <t>9703511099</t>
-        </is>
+      <c r="O17" s="3" t="n">
+        <v>9703511099</v>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
@@ -4288,25 +4270,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN17" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN17" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO17" s="3" t="inlineStr">
         <is>
           <t>CDB401</t>
         </is>
       </c>
-      <c r="AP17" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP17" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ17" s="3" t="inlineStr"/>
       <c r="AR17" s="3" t="inlineStr">
         <is>
-          <t>Case : 5g name not showing   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS17" s="3" t="inlineStr">
@@ -4407,10 +4385,8 @@
           <t>Sangita Shrestha</t>
         </is>
       </c>
-      <c r="O18" s="3" t="inlineStr">
-        <is>
-          <t>9841525749</t>
-        </is>
+      <c r="O18" s="3" t="n">
+        <v>9841525749</v>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
@@ -4504,25 +4480,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN18" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN18" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO18" s="3" t="inlineStr">
         <is>
           <t>3,6</t>
         </is>
       </c>
-      <c r="AP18" s="3" t="inlineStr">
-        <is>
-          <t>85.2875</t>
-        </is>
+      <c r="AP18" s="3" t="n">
+        <v>85.28749999999999</v>
       </c>
       <c r="AQ18" s="3" t="inlineStr"/>
       <c r="AR18" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS18" s="3" t="inlineStr">
@@ -4623,10 +4595,8 @@
           <t>Sangita Shrestha</t>
         </is>
       </c>
-      <c r="O19" s="3" t="inlineStr">
-        <is>
-          <t>9841525749</t>
-        </is>
+      <c r="O19" s="3" t="n">
+        <v>9841525749</v>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
@@ -4720,25 +4690,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN19" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN19" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO19" s="3" t="inlineStr">
         <is>
           <t>3,6</t>
         </is>
       </c>
-      <c r="AP19" s="3" t="inlineStr">
-        <is>
-          <t>85.2875</t>
-        </is>
+      <c r="AP19" s="3" t="n">
+        <v>85.28749999999999</v>
       </c>
       <c r="AQ19" s="3" t="inlineStr"/>
       <c r="AR19" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS19" s="3" t="inlineStr">
@@ -4839,10 +4805,8 @@
           <t>Shyam Shrestha</t>
         </is>
       </c>
-      <c r="O20" s="3" t="inlineStr">
-        <is>
-          <t>9860959933</t>
-        </is>
+      <c r="O20" s="3" t="n">
+        <v>9860959933</v>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
@@ -4936,53 +4900,473 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN20" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN20" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO20" s="3" t="inlineStr">
         <is>
           <t>CDB196</t>
         </is>
       </c>
-      <c r="AP20" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP20" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ20" s="3" t="inlineStr"/>
       <c r="AR20" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS20" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 28m</t>
+        </is>
+      </c>
+      <c r="AT20" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 28m</t>
+        </is>
+      </c>
+      <c r="AU20" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV20" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS20" s="3" t="inlineStr">
-        <is>
-          <t>1d 2h 28m</t>
-        </is>
-      </c>
-      <c r="AT20" s="3" t="inlineStr">
-        <is>
-          <t>1d 2h 28m</t>
-        </is>
-      </c>
-      <c r="AU20" s="3" t="inlineStr">
+      <c r="AW20" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX20" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 2:11 PM</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Case : Roueter Upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>Roueter Upgrade</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>TKT1370819</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>Mahesh kumar dahal</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>Mahesh kumar dahal</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>9851100862</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q21" s="3" t="inlineStr"/>
+      <c r="R21" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 02:11:23 PM</t>
+        </is>
+      </c>
+      <c r="S21" s="3" t="inlineStr"/>
+      <c r="T21" s="3" t="inlineStr"/>
+      <c r="U21" s="3" t="inlineStr">
+        <is>
+          <t>9851100862</t>
+        </is>
+      </c>
+      <c r="V21" s="3" t="inlineStr">
+        <is>
+          <t>14 Oct 2026 04:07:37 PM</t>
+        </is>
+      </c>
+      <c r="W21" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 02:11:23 PM</t>
+        </is>
+      </c>
+      <c r="X21" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y21" s="3" t="inlineStr">
+        <is>
+          <t>27.68453</t>
+        </is>
+      </c>
+      <c r="Z21" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA21" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB21" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC21" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD21" s="3" t="inlineStr"/>
+      <c r="AE21" s="3" t="inlineStr">
+        <is>
+          <t>Sanepa ( Inside Ring Road ) Beside phoenix school, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF21" s="3" t="inlineStr">
+        <is>
+          <t>krmahesh009@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG21" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH21" s="3" t="inlineStr"/>
+      <c r="AI21" s="3" t="inlineStr">
+        <is>
+          <t>08:04 hour</t>
+        </is>
+      </c>
+      <c r="AJ21" s="3" t="inlineStr"/>
+      <c r="AK21" s="3" t="inlineStr"/>
+      <c r="AL21" s="3" t="inlineStr">
+        <is>
+          <t>Biraj Thapa</t>
+        </is>
+      </c>
+      <c r="AM21" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN21" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO21" s="3" t="inlineStr">
+        <is>
+          <t>CDB673</t>
+        </is>
+      </c>
+      <c r="AP21" s="3" t="inlineStr">
+        <is>
+          <t>85.30329</t>
+        </is>
+      </c>
+      <c r="AQ21" s="3" t="inlineStr"/>
+      <c r="AR21" s="3" t="inlineStr">
+        <is>
+          <t>Case : Roueter Upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS21" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT21" s="3" t="inlineStr">
+        <is>
+          <t>22h 3m</t>
+        </is>
+      </c>
+      <c r="AU21" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV21" s="3" t="inlineStr">
+        <is>
+          <t>Case : Roueter Upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW21" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX21" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 2:02 PM</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr"/>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Case : light issue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>light issue</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>TKT1371490</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>Kamala Limbu</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>Kamala Limbu</t>
+        </is>
+      </c>
+      <c r="O22" s="3" t="inlineStr">
+        <is>
+          <t>9767264992</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q22" s="3" t="inlineStr"/>
+      <c r="R22" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 10:23:07 AM</t>
+        </is>
+      </c>
+      <c r="S22" s="3" t="inlineStr"/>
+      <c r="T22" s="3" t="inlineStr"/>
+      <c r="U22" s="3" t="inlineStr">
+        <is>
+          <t>KLK9767264992</t>
+        </is>
+      </c>
+      <c r="V22" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 10:12:14 AM</t>
+        </is>
+      </c>
+      <c r="W22" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 02:02:22 PM</t>
+        </is>
+      </c>
+      <c r="X22" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y22" s="3" t="inlineStr"/>
+      <c r="Z22" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA22" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB22" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC22" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD22" s="3" t="inlineStr"/>
+      <c r="AE22" s="3" t="inlineStr">
+        <is>
+          <t>near by Mahendra Ratna Campus - Government college Museum Marg Kathmandu 44600, Kathmandu, Nepal, Ne</t>
+        </is>
+      </c>
+      <c r="AF22" s="3" t="inlineStr">
+        <is>
+          <t>9767264992@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG22" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH22" s="3" t="inlineStr"/>
+      <c r="AI22" s="3" t="inlineStr">
+        <is>
+          <t>03:50 hour</t>
+        </is>
+      </c>
+      <c r="AJ22" s="3" t="inlineStr"/>
+      <c r="AK22" s="3" t="inlineStr"/>
+      <c r="AL22" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM22" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN22" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO22" s="3" t="inlineStr">
+        <is>
+          <t>CDB136</t>
+        </is>
+      </c>
+      <c r="AP22" s="3" t="inlineStr"/>
+      <c r="AQ22" s="3" t="inlineStr"/>
+      <c r="AR22" s="3" t="inlineStr">
+        <is>
+          <t>Case : light issue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS22" s="3" t="inlineStr">
+        <is>
+          <t>3h 39m</t>
+        </is>
+      </c>
+      <c r="AT22" s="3" t="inlineStr">
+        <is>
+          <t>3h 50m</t>
+        </is>
+      </c>
+      <c r="AU22" s="3" t="inlineStr">
         <is>
           <t>Completed (Closed)</t>
         </is>
       </c>
-      <c r="AV20" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
-      <c r="AW20" s="3" t="inlineStr">
-        <is>
-          <t>WiFi 6 Upgrade</t>
-        </is>
-      </c>
-      <c r="AX20" s="3" t="inlineStr">
+      <c r="AV22" s="3" t="inlineStr">
+        <is>
+          <t>Case : light issue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW22" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX22" s="3" t="inlineStr">
         <is>
           <t>Sunil Chaudhary</t>
         </is>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_15_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_15_Oct_2026.xlsx
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>81.0%</t>
+          <t>82.6%</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>26.1%</t>
         </is>
       </c>
     </row>
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>13.0%</t>
         </is>
       </c>
     </row>
@@ -734,10 +734,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>47.8%</t>
         </is>
       </c>
     </row>
@@ -761,7 +761,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -817,13 +817,13 @@
         <v>0</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3">
@@ -851,7 +851,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Configuration Issue</t>
+          <t>IPTV Remote damage Issue</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -861,10 +861,10 @@
         <v>0</v>
       </c>
       <c r="D4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="F4" s="6" t="n">
         <v>1</v>
@@ -873,7 +873,7 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>IPTV Remote damage Issue</t>
+          <t>Configuration Issue</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -883,10 +883,10 @@
         <v>0</v>
       </c>
       <c r="D5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="F5" s="6" t="n">
         <v>1</v>
@@ -939,17 +939,17 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>SKYCOM-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="E8" s="3" t="n">
         <v>0</v>
@@ -959,25 +959,47 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n">
+      <c r="B10" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="C9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="E9" s="4" t="n">
+      <c r="C10" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="E10" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="F9" s="4" t="n">
-        <v>17</v>
+      <c r="F10" s="4" t="n">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -991,7 +1013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX22"/>
+  <dimension ref="A1:AX24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1031,7 +1053,7 @@
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="19" customWidth="1" min="38" max="38"/>
+    <col width="28" customWidth="1" min="38" max="38"/>
     <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
@@ -5015,10 +5037,8 @@
           <t>Mahesh kumar dahal</t>
         </is>
       </c>
-      <c r="O21" s="3" t="inlineStr">
-        <is>
-          <t>9851100862</t>
-        </is>
+      <c r="O21" s="3" t="n">
+        <v>9851100862</v>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
@@ -5112,25 +5132,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN21" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN21" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO21" s="3" t="inlineStr">
         <is>
           <t>CDB673</t>
         </is>
       </c>
-      <c r="AP21" s="3" t="inlineStr">
-        <is>
-          <t>85.30329</t>
-        </is>
+      <c r="AP21" s="3" t="n">
+        <v>85.30329</v>
       </c>
       <c r="AQ21" s="3" t="inlineStr"/>
       <c r="AR21" s="3" t="inlineStr">
         <is>
-          <t>Case : Roueter Upgrade  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS21" s="3" t="inlineStr">
@@ -5231,10 +5247,8 @@
           <t>Kamala Limbu</t>
         </is>
       </c>
-      <c r="O22" s="3" t="inlineStr">
-        <is>
-          <t>9767264992</t>
-        </is>
+      <c r="O22" s="3" t="n">
+        <v>9767264992</v>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
@@ -5324,10 +5338,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN22" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN22" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO22" s="3" t="inlineStr">
         <is>
@@ -5338,29 +5350,29 @@
       <c r="AQ22" s="3" t="inlineStr"/>
       <c r="AR22" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS22" s="3" t="inlineStr">
+        <is>
+          <t>3h 39m</t>
+        </is>
+      </c>
+      <c r="AT22" s="3" t="inlineStr">
+        <is>
+          <t>3h 50m</t>
+        </is>
+      </c>
+      <c r="AU22" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV22" s="3" t="inlineStr">
+        <is>
           <t>Case : light issue  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS22" s="3" t="inlineStr">
-        <is>
-          <t>3h 39m</t>
-        </is>
-      </c>
-      <c r="AT22" s="3" t="inlineStr">
-        <is>
-          <t>3h 50m</t>
-        </is>
-      </c>
-      <c r="AU22" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV22" s="3" t="inlineStr">
-        <is>
-          <t>Case : light issue  has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
       <c r="AW22" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
@@ -5369,6 +5381,438 @@
       <c r="AX22" s="3" t="inlineStr">
         <is>
           <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 2:26 PM</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr"/>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>TKT1371583</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>Sushil khatiwada</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t>Sushil khatiwada</t>
+        </is>
+      </c>
+      <c r="O23" s="3" t="inlineStr">
+        <is>
+          <t>9841465375</t>
+        </is>
+      </c>
+      <c r="P23" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q23" s="3" t="inlineStr"/>
+      <c r="R23" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 02:26:50 PM</t>
+        </is>
+      </c>
+      <c r="S23" s="3" t="inlineStr"/>
+      <c r="T23" s="3" t="inlineStr"/>
+      <c r="U23" s="3" t="inlineStr">
+        <is>
+          <t>9841465375</t>
+        </is>
+      </c>
+      <c r="V23" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 11:12:54 AM</t>
+        </is>
+      </c>
+      <c r="W23" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 02:26:50 PM</t>
+        </is>
+      </c>
+      <c r="X23" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y23" s="3" t="inlineStr">
+        <is>
+          <t>27.65884</t>
+        </is>
+      </c>
+      <c r="Z23" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA23" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB23" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC23" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD23" s="3" t="inlineStr"/>
+      <c r="AE23" s="3" t="inlineStr">
+        <is>
+          <t>Imadol Near New Bhadrakali Petrol Pump, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF23" s="3" t="inlineStr">
+        <is>
+          <t>peace.sushil@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG23" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH23" s="3" t="inlineStr"/>
+      <c r="AI23" s="3" t="inlineStr">
+        <is>
+          <t>03:14 hour</t>
+        </is>
+      </c>
+      <c r="AJ23" s="3" t="inlineStr"/>
+      <c r="AK23" s="3" t="inlineStr"/>
+      <c r="AL23" s="3" t="inlineStr">
+        <is>
+          <t>Sabina K.C</t>
+        </is>
+      </c>
+      <c r="AM23" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN23" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO23" s="3" t="inlineStr">
+        <is>
+          <t>3,1</t>
+        </is>
+      </c>
+      <c r="AP23" s="3" t="inlineStr">
+        <is>
+          <t>85.34781</t>
+        </is>
+      </c>
+      <c r="AQ23" s="3" t="inlineStr"/>
+      <c r="AR23" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS23" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT23" s="3" t="inlineStr">
+        <is>
+          <t>3h 13m</t>
+        </is>
+      </c>
+      <c r="AU23" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV23" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW23" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX23" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 2:25 PM</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr"/>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>IPTV ISSUE</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>TKT1369775</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>Madhu Thapaliya</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>Madhu Thapaliya</t>
+        </is>
+      </c>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t>9841266846</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q24" s="3" t="inlineStr"/>
+      <c r="R24" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 02:25:19 PM</t>
+        </is>
+      </c>
+      <c r="S24" s="3" t="inlineStr"/>
+      <c r="T24" s="3" t="inlineStr"/>
+      <c r="U24" s="3" t="inlineStr">
+        <is>
+          <t>9841266846</t>
+        </is>
+      </c>
+      <c r="V24" s="3" t="inlineStr">
+        <is>
+          <t>14 Oct 2026 06:29:07 AM</t>
+        </is>
+      </c>
+      <c r="W24" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 02:25:19 PM</t>
+        </is>
+      </c>
+      <c r="X24" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y24" s="3" t="inlineStr">
+        <is>
+          <t>27.744145</t>
+        </is>
+      </c>
+      <c r="Z24" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA24" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB24" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC24" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD24" s="3" t="inlineStr"/>
+      <c r="AE24" s="3" t="inlineStr">
+        <is>
+          <t>Nirmalbatika school, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF24" s="3" t="inlineStr">
+        <is>
+          <t>madhu22@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG24" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="AH24" s="3" t="inlineStr"/>
+      <c r="AI24" s="3" t="inlineStr">
+        <is>
+          <t>14:25 hour</t>
+        </is>
+      </c>
+      <c r="AJ24" s="3" t="inlineStr"/>
+      <c r="AK24" s="3" t="inlineStr"/>
+      <c r="AL24" s="3" t="inlineStr">
+        <is>
+          <t>Roshan Yadav (L1 Support)</t>
+        </is>
+      </c>
+      <c r="AM24" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN24" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO24" s="3" t="inlineStr">
+        <is>
+          <t>L19-8</t>
+        </is>
+      </c>
+      <c r="AP24" s="3" t="inlineStr">
+        <is>
+          <t>85.320073</t>
+        </is>
+      </c>
+      <c r="AQ24" s="3" t="inlineStr"/>
+      <c r="AR24" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS24" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT24" s="3" t="inlineStr">
+        <is>
+          <t>1d 7h 56m</t>
+        </is>
+      </c>
+      <c r="AU24" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV24" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW24" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX24" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_15_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_15_Oct_2026.xlsx
@@ -532,10 +532,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>82.6%</t>
+          <t>84.0%</t>
         </is>
       </c>
     </row>
@@ -688,10 +688,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
@@ -700,7 +700,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>26.1%</t>
+          <t>28.0%</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>12.0%</t>
         </is>
       </c>
     </row>
@@ -734,10 +734,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>48.0%</t>
         </is>
       </c>
     </row>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>5</v>
@@ -823,7 +823,7 @@
         <v>2</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3">
@@ -987,10 +987,10 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" s="4" t="n">
         <v>8</v>
@@ -999,7 +999,7 @@
         <v>5</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -1013,7 +1013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX24"/>
+  <dimension ref="A1:AX26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -5451,10 +5451,8 @@
           <t>Sushil khatiwada</t>
         </is>
       </c>
-      <c r="O23" s="3" t="inlineStr">
-        <is>
-          <t>9841465375</t>
-        </is>
+      <c r="O23" s="3" t="n">
+        <v>9841465375</v>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
@@ -5548,25 +5546,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN23" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN23" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO23" s="3" t="inlineStr">
         <is>
           <t>3,1</t>
         </is>
       </c>
-      <c r="AP23" s="3" t="inlineStr">
-        <is>
-          <t>85.34781</t>
-        </is>
+      <c r="AP23" s="3" t="n">
+        <v>85.34781</v>
       </c>
       <c r="AQ23" s="3" t="inlineStr"/>
       <c r="AR23" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS23" s="3" t="inlineStr">
@@ -5667,10 +5661,8 @@
           <t>Madhu Thapaliya</t>
         </is>
       </c>
-      <c r="O24" s="3" t="inlineStr">
-        <is>
-          <t>9841266846</t>
-        </is>
+      <c r="O24" s="3" t="n">
+        <v>9841266846</v>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
@@ -5764,55 +5756,471 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN24" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN24" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO24" s="3" t="inlineStr">
         <is>
           <t>L19-8</t>
         </is>
       </c>
-      <c r="AP24" s="3" t="inlineStr">
-        <is>
-          <t>85.320073</t>
-        </is>
+      <c r="AP24" s="3" t="n">
+        <v>85.32007299999999</v>
       </c>
       <c r="AQ24" s="3" t="inlineStr"/>
       <c r="AR24" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS24" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT24" s="3" t="inlineStr">
+        <is>
+          <t>1d 7h 56m</t>
+        </is>
+      </c>
+      <c r="AU24" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV24" s="3" t="inlineStr">
+        <is>
           <t>Case : IPTV ISSUE   has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AS24" s="3" t="inlineStr">
+      <c r="AW24" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX24" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 2:39 PM</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr"/>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>Case : call back  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>call back</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>TKT1364194</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>Tula Bahadur Tamang</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t>Tula Bahadur Tamang</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
+          <t>9803074170</t>
+        </is>
+      </c>
+      <c r="P25" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q25" s="3" t="inlineStr"/>
+      <c r="R25" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 02:39:49 PM</t>
+        </is>
+      </c>
+      <c r="S25" s="3" t="inlineStr"/>
+      <c r="T25" s="3" t="inlineStr"/>
+      <c r="U25" s="3" t="inlineStr">
+        <is>
+          <t>9845065030</t>
+        </is>
+      </c>
+      <c r="V25" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 09:50:33 AM</t>
+        </is>
+      </c>
+      <c r="W25" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 02:39:49 PM</t>
+        </is>
+      </c>
+      <c r="X25" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y25" s="3" t="inlineStr">
+        <is>
+          <t>27.74616</t>
+        </is>
+      </c>
+      <c r="Z25" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA25" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB25" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC25" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD25" s="3" t="inlineStr"/>
+      <c r="AE25" s="3" t="inlineStr">
+        <is>
+          <t>opoosite bhathbhateni tokha, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF25" s="3" t="inlineStr">
+        <is>
+          <t>tulatamang13@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG25" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH25" s="3" t="inlineStr"/>
+      <c r="AI25" s="3" t="inlineStr">
+        <is>
+          <t>06:39 hour</t>
+        </is>
+      </c>
+      <c r="AJ25" s="3" t="inlineStr"/>
+      <c r="AK25" s="3" t="inlineStr"/>
+      <c r="AL25" s="3" t="inlineStr">
+        <is>
+          <t>Joshna Shrestha</t>
+        </is>
+      </c>
+      <c r="AM25" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN25" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO25" s="3" t="inlineStr">
+        <is>
+          <t>1,1</t>
+        </is>
+      </c>
+      <c r="AP25" s="3" t="inlineStr">
+        <is>
+          <t>85.32389</t>
+        </is>
+      </c>
+      <c r="AQ25" s="3" t="inlineStr"/>
+      <c r="AR25" s="3" t="inlineStr">
+        <is>
+          <t>Case : call back  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS25" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT24" s="3" t="inlineStr">
-        <is>
-          <t>1d 7h 56m</t>
-        </is>
-      </c>
-      <c r="AU24" s="3" t="inlineStr">
+      <c r="AT25" s="3" t="inlineStr">
+        <is>
+          <t>6d 4h 49m</t>
+        </is>
+      </c>
+      <c r="AU25" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV24" s="3" t="inlineStr">
-        <is>
-          <t>Case : IPTV ISSUE   has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="AW24" s="3" t="inlineStr">
-        <is>
-          <t>IPTV Issue</t>
-        </is>
-      </c>
-      <c r="AX24" s="3" t="inlineStr">
+      <c r="AV25" s="3" t="inlineStr">
+        <is>
+          <t>Case : call back  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW25" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX25" s="3" t="inlineStr">
         <is>
           <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 2:46 PM</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr"/>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>TKT1370740</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>Kamala Malla</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t>Kamala Malla</t>
+        </is>
+      </c>
+      <c r="O26" s="3" t="inlineStr">
+        <is>
+          <t>9813043644</t>
+        </is>
+      </c>
+      <c r="P26" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q26" s="3" t="inlineStr"/>
+      <c r="R26" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 02:46:39 PM</t>
+        </is>
+      </c>
+      <c r="S26" s="3" t="inlineStr"/>
+      <c r="T26" s="3" t="inlineStr"/>
+      <c r="U26" s="3" t="inlineStr">
+        <is>
+          <t>9813043644</t>
+        </is>
+      </c>
+      <c r="V26" s="3" t="inlineStr">
+        <is>
+          <t>14 Oct 2026 03:38:38 PM</t>
+        </is>
+      </c>
+      <c r="W26" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 02:46:39 PM</t>
+        </is>
+      </c>
+      <c r="X26" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y26" s="3" t="inlineStr"/>
+      <c r="Z26" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA26" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB26" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC26" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD26" s="3" t="inlineStr"/>
+      <c r="AE26" s="3" t="inlineStr">
+        <is>
+          <t>Dhobighat, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF26" s="3" t="inlineStr"/>
+      <c r="AG26" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH26" s="3" t="inlineStr"/>
+      <c r="AI26" s="3" t="inlineStr">
+        <is>
+          <t>09:08 hour</t>
+        </is>
+      </c>
+      <c r="AJ26" s="3" t="inlineStr"/>
+      <c r="AK26" s="3" t="inlineStr"/>
+      <c r="AL26" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM26" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN26" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO26" s="3" t="inlineStr">
+        <is>
+          <t>CDB381</t>
+        </is>
+      </c>
+      <c r="AP26" s="3" t="inlineStr"/>
+      <c r="AQ26" s="3" t="inlineStr"/>
+      <c r="AR26" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS26" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT26" s="3" t="inlineStr">
+        <is>
+          <t>23h 8m</t>
+        </is>
+      </c>
+      <c r="AU26" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV26" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW26" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX26" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_15_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_15_Oct_2026.xlsx
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>6</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>84.0%</t>
+          <t>81.5%</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>28.0%</t>
+          <t>25.9%</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>11.1%</t>
         </is>
       </c>
     </row>
@@ -734,10 +734,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>48.1%</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
         <v>5</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>5</v>
@@ -823,7 +823,7 @@
         <v>2</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
@@ -990,7 +990,7 @@
         <v>5</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D10" s="4" t="n">
         <v>8</v>
@@ -999,7 +999,7 @@
         <v>5</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -1013,7 +1013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX26"/>
+  <dimension ref="A1:AX28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -5871,10 +5871,8 @@
           <t>Tula Bahadur Tamang</t>
         </is>
       </c>
-      <c r="O25" s="3" t="inlineStr">
-        <is>
-          <t>9803074170</t>
-        </is>
+      <c r="O25" s="3" t="n">
+        <v>9803074170</v>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
@@ -5968,25 +5966,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN25" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN25" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO25" s="3" t="inlineStr">
         <is>
           <t>1,1</t>
         </is>
       </c>
-      <c r="AP25" s="3" t="inlineStr">
-        <is>
-          <t>85.32389</t>
-        </is>
+      <c r="AP25" s="3" t="n">
+        <v>85.32389000000001</v>
       </c>
       <c r="AQ25" s="3" t="inlineStr"/>
       <c r="AR25" s="3" t="inlineStr">
         <is>
-          <t>Case : call back  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS25" s="3" t="inlineStr">
@@ -6087,10 +6081,8 @@
           <t>Kamala Malla</t>
         </is>
       </c>
-      <c r="O26" s="3" t="inlineStr">
-        <is>
-          <t>9813043644</t>
-        </is>
+      <c r="O26" s="3" t="n">
+        <v>9813043644</v>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
@@ -6176,10 +6168,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN26" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN26" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO26" s="3" t="inlineStr">
         <is>
@@ -6190,37 +6180,357 @@
       <c r="AQ26" s="3" t="inlineStr"/>
       <c r="AR26" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS26" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT26" s="3" t="inlineStr">
+        <is>
+          <t>23h 8m</t>
+        </is>
+      </c>
+      <c r="AU26" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV26" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AS26" s="3" t="inlineStr">
+      <c r="AW26" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX26" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 2:54 PM</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr"/>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>TKT1370586</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>Prakash Pangeni</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t>Prakash Pangeni</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t>9841857950</t>
+        </is>
+      </c>
+      <c r="P27" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q27" s="3" t="inlineStr"/>
+      <c r="R27" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 02:54:20 PM</t>
+        </is>
+      </c>
+      <c r="S27" s="3" t="inlineStr"/>
+      <c r="T27" s="3" t="inlineStr"/>
+      <c r="U27" s="3" t="inlineStr">
+        <is>
+          <t>DRZ9841857950</t>
+        </is>
+      </c>
+      <c r="V27" s="3" t="inlineStr">
+        <is>
+          <t>14 Oct 2026 02:20:43 PM</t>
+        </is>
+      </c>
+      <c r="W27" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 02:54:20 PM</t>
+        </is>
+      </c>
+      <c r="X27" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y27" s="3" t="inlineStr">
+        <is>
+          <t>27.75684</t>
+        </is>
+      </c>
+      <c r="Z27" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA27" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB27" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC27" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD27" s="3" t="inlineStr"/>
+      <c r="AE27" s="3" t="inlineStr">
+        <is>
+          <t>suryadarshan height micro park. Bagmati Province, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF27" s="3" t="inlineStr"/>
+      <c r="AG27" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH27" s="3" t="inlineStr"/>
+      <c r="AI27" s="3" t="inlineStr">
+        <is>
+          <t>10:34 hour</t>
+        </is>
+      </c>
+      <c r="AJ27" s="3" t="inlineStr"/>
+      <c r="AK27" s="3" t="inlineStr"/>
+      <c r="AL27" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM27" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN27" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO27" s="3" t="inlineStr">
+        <is>
+          <t>L36-7</t>
+        </is>
+      </c>
+      <c r="AP27" s="3" t="inlineStr">
+        <is>
+          <t>85.3222</t>
+        </is>
+      </c>
+      <c r="AQ27" s="3" t="inlineStr"/>
+      <c r="AR27" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS27" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT26" s="3" t="inlineStr">
-        <is>
-          <t>23h 8m</t>
-        </is>
-      </c>
-      <c r="AU26" s="3" t="inlineStr">
+      <c r="AT27" s="3" t="inlineStr">
+        <is>
+          <t>1d 33m</t>
+        </is>
+      </c>
+      <c r="AU27" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV26" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
-      <c r="AW26" s="3" t="inlineStr">
+      <c r="AV27" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW27" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="AX26" s="3" t="inlineStr">
-        <is>
-          <t>Rajesh Maharjan</t>
+      <c r="AX27" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 2:59 PM</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr"/>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr"/>
+      <c r="J28" s="3" t="inlineStr"/>
+      <c r="K28" s="3" t="inlineStr"/>
+      <c r="L28" s="3" t="inlineStr"/>
+      <c r="M28" s="3" t="inlineStr"/>
+      <c r="N28" s="3" t="inlineStr"/>
+      <c r="O28" s="3" t="inlineStr"/>
+      <c r="P28" s="3" t="inlineStr"/>
+      <c r="Q28" s="3" t="inlineStr"/>
+      <c r="R28" s="3" t="inlineStr"/>
+      <c r="S28" s="3" t="inlineStr"/>
+      <c r="T28" s="3" t="inlineStr"/>
+      <c r="U28" s="3" t="inlineStr"/>
+      <c r="V28" s="3" t="inlineStr"/>
+      <c r="W28" s="3" t="inlineStr"/>
+      <c r="X28" s="3" t="inlineStr"/>
+      <c r="Y28" s="3" t="inlineStr"/>
+      <c r="Z28" s="3" t="inlineStr"/>
+      <c r="AA28" s="3" t="inlineStr"/>
+      <c r="AB28" s="3" t="inlineStr"/>
+      <c r="AC28" s="3" t="inlineStr"/>
+      <c r="AD28" s="3" t="inlineStr"/>
+      <c r="AE28" s="3" t="inlineStr"/>
+      <c r="AF28" s="3" t="inlineStr"/>
+      <c r="AG28" s="3" t="inlineStr"/>
+      <c r="AH28" s="3" t="inlineStr"/>
+      <c r="AI28" s="3" t="inlineStr"/>
+      <c r="AJ28" s="3" t="inlineStr"/>
+      <c r="AK28" s="3" t="inlineStr"/>
+      <c r="AL28" s="3" t="inlineStr"/>
+      <c r="AM28" s="3" t="inlineStr"/>
+      <c r="AN28" s="3" t="inlineStr"/>
+      <c r="AO28" s="3" t="inlineStr"/>
+      <c r="AP28" s="3" t="inlineStr"/>
+      <c r="AQ28" s="3" t="inlineStr"/>
+      <c r="AR28" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS28" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT28" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU28" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV28" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW28" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX28" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_15_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_15_Oct_2026.xlsx
@@ -1059,7 +1059,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -6281,10 +6281,8 @@
           <t>Prakash Pangeni</t>
         </is>
       </c>
-      <c r="O27" s="3" t="inlineStr">
-        <is>
-          <t>9841857950</t>
-        </is>
+      <c r="O27" s="3" t="n">
+        <v>9841857950</v>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
@@ -6374,25 +6372,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN27" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN27" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO27" s="3" t="inlineStr">
         <is>
           <t>L36-7</t>
         </is>
       </c>
-      <c r="AP27" s="3" t="inlineStr">
-        <is>
-          <t>85.3222</t>
-        </is>
+      <c r="AP27" s="3" t="n">
+        <v>85.3222</v>
       </c>
       <c r="AQ27" s="3" t="inlineStr"/>
       <c r="AR27" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS27" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_15_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_15_Oct_2026.xlsx
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>6</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>81.5%</t>
+          <t>79.3%</t>
         </is>
       </c>
     </row>
@@ -688,10 +688,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
@@ -700,7 +700,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>27.6%</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>10.3%</t>
         </is>
       </c>
     </row>
@@ -734,19 +734,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>13</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>92.9%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>48.3%</t>
         </is>
       </c>
     </row>
@@ -817,19 +817,19 @@
         <v>2</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Configuration Issue</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -851,29 +851,29 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>IPTV Remote damage Issue</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="E4" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E4" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="F4" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Configuration Issue</t>
+          <t>IPTV Remote damage Issue</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -883,10 +883,10 @@
         <v>0</v>
       </c>
       <c r="D5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="F5" s="6" t="n">
         <v>1</v>
@@ -990,16 +990,16 @@
         <v>5</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E10" s="4" t="n">
         <v>5</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -1013,7 +1013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX28"/>
+  <dimension ref="A1:AX30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1047,7 +1047,7 @@
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
-    <col width="25" customWidth="1" min="32" max="32"/>
+    <col width="27" customWidth="1" min="32" max="32"/>
     <col width="30" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
@@ -1059,7 +1059,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -6528,6 +6528,418 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 3:37 PM</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr"/>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>Case : no internet issue   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>no internet issue</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>TKT1371779</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>Holly bell girls hostel</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t>Holly bell girls hostel</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="inlineStr">
+        <is>
+          <t>9823665014</t>
+        </is>
+      </c>
+      <c r="P29" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q29" s="3" t="inlineStr"/>
+      <c r="R29" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 03:37:07 PM</t>
+        </is>
+      </c>
+      <c r="S29" s="3" t="inlineStr"/>
+      <c r="T29" s="3" t="inlineStr"/>
+      <c r="U29" s="3" t="inlineStr">
+        <is>
+          <t>CHB9823665014</t>
+        </is>
+      </c>
+      <c r="V29" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 01:50:08 PM</t>
+        </is>
+      </c>
+      <c r="W29" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 03:37:07 PM</t>
+        </is>
+      </c>
+      <c r="X29" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y29" s="3" t="inlineStr"/>
+      <c r="Z29" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA29" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB29" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC29" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD29" s="3" t="inlineStr"/>
+      <c r="AE29" s="3" t="inlineStr">
+        <is>
+          <t>Basundhara,chauki, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF29" s="3" t="inlineStr">
+        <is>
+          <t>aaaaa@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG29" s="3" t="inlineStr">
+        <is>
+          <t>Configuration Issue</t>
+        </is>
+      </c>
+      <c r="AH29" s="3" t="inlineStr"/>
+      <c r="AI29" s="3" t="inlineStr">
+        <is>
+          <t>01:47 hour</t>
+        </is>
+      </c>
+      <c r="AJ29" s="3" t="inlineStr"/>
+      <c r="AK29" s="3" t="inlineStr"/>
+      <c r="AL29" s="3" t="inlineStr">
+        <is>
+          <t>Rahul Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM29" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN29" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO29" s="3" t="inlineStr">
+        <is>
+          <t>L36-3</t>
+        </is>
+      </c>
+      <c r="AP29" s="3" t="inlineStr"/>
+      <c r="AQ29" s="3" t="inlineStr"/>
+      <c r="AR29" s="3" t="inlineStr">
+        <is>
+          <t>Case : no internet issue   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS29" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT29" s="3" t="inlineStr">
+        <is>
+          <t>1h 46m</t>
+        </is>
+      </c>
+      <c r="AU29" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV29" s="3" t="inlineStr">
+        <is>
+          <t>Case : no internet issue   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW29" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX29" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 3:21 PM</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr"/>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>TKT1371820</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>Madav Nepal</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
+          <t>Madav Nepal</t>
+        </is>
+      </c>
+      <c r="O30" s="3" t="inlineStr">
+        <is>
+          <t>9767384015</t>
+        </is>
+      </c>
+      <c r="P30" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q30" s="3" t="inlineStr"/>
+      <c r="R30" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 02:23:45 PM</t>
+        </is>
+      </c>
+      <c r="S30" s="3" t="inlineStr"/>
+      <c r="T30" s="3" t="inlineStr"/>
+      <c r="U30" s="3" t="inlineStr">
+        <is>
+          <t>BKT9767384015</t>
+        </is>
+      </c>
+      <c r="V30" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 02:23:45 PM</t>
+        </is>
+      </c>
+      <c r="W30" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 03:21:26 PM</t>
+        </is>
+      </c>
+      <c r="X30" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y30" s="3" t="inlineStr"/>
+      <c r="Z30" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA30" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB30" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC30" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD30" s="3" t="inlineStr"/>
+      <c r="AE30" s="3" t="inlineStr">
+        <is>
+          <t>27.668574009940066, 85.37675397961262 GPS Coordinates Nearest: BKT002-01-1/7-L7-5 (76m Road) Map: CG</t>
+        </is>
+      </c>
+      <c r="AF30" s="3" t="inlineStr">
+        <is>
+          <t>madhavnepal916@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG30" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH30" s="3" t="inlineStr"/>
+      <c r="AI30" s="3" t="inlineStr"/>
+      <c r="AJ30" s="3" t="inlineStr"/>
+      <c r="AK30" s="3" t="inlineStr"/>
+      <c r="AL30" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM30" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN30" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO30" s="3" t="inlineStr">
+        <is>
+          <t>L7-7A</t>
+        </is>
+      </c>
+      <c r="AP30" s="3" t="inlineStr"/>
+      <c r="AQ30" s="3" t="inlineStr"/>
+      <c r="AR30" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS30" s="3" t="inlineStr">
+        <is>
+          <t>57m</t>
+        </is>
+      </c>
+      <c r="AT30" s="3" t="inlineStr">
+        <is>
+          <t>57m</t>
+        </is>
+      </c>
+      <c r="AU30" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV30" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW30" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX30" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_15_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_15_Oct_2026.xlsx
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>6</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>54.5%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>23</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>79.3%</t>
+          <t>76.7%</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>26.7%</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>10.0%</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>48.3%</t>
+          <t>46.7%</t>
         </is>
       </c>
     </row>
@@ -1013,7 +1013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX30"/>
+  <dimension ref="A1:AX31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1059,7 +1059,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -6595,10 +6595,8 @@
           <t>Holly bell girls hostel</t>
         </is>
       </c>
-      <c r="O29" s="3" t="inlineStr">
-        <is>
-          <t>9823665014</t>
-        </is>
+      <c r="O29" s="3" t="n">
+        <v>9823665014</v>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
@@ -6688,10 +6686,8 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN29" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN29" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO29" s="3" t="inlineStr">
         <is>
@@ -6702,7 +6698,7 @@
       <c r="AQ29" s="3" t="inlineStr"/>
       <c r="AR29" s="3" t="inlineStr">
         <is>
-          <t>Case : no internet issue   has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS29" s="3" t="inlineStr">
@@ -6803,10 +6799,8 @@
           <t>Madav Nepal</t>
         </is>
       </c>
-      <c r="O30" s="3" t="inlineStr">
-        <is>
-          <t>9767384015</t>
-        </is>
+      <c r="O30" s="3" t="n">
+        <v>9767384015</v>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
@@ -6892,10 +6886,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN30" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN30" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO30" s="3" t="inlineStr">
         <is>
@@ -6906,35 +6898,143 @@
       <c r="AQ30" s="3" t="inlineStr"/>
       <c r="AR30" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS30" s="3" t="inlineStr">
+        <is>
+          <t>57m</t>
+        </is>
+      </c>
+      <c r="AT30" s="3" t="inlineStr">
+        <is>
+          <t>57m</t>
+        </is>
+      </c>
+      <c r="AU30" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV30" s="3" t="inlineStr">
+        <is>
           <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS30" s="3" t="inlineStr">
-        <is>
-          <t>57m</t>
-        </is>
-      </c>
-      <c r="AT30" s="3" t="inlineStr">
-        <is>
-          <t>57m</t>
-        </is>
-      </c>
-      <c r="AU30" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (On Hold)</t>
-        </is>
-      </c>
-      <c r="AV30" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
       <c r="AW30" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
       <c r="AX30" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 3:53 PM</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr"/>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr"/>
+      <c r="J31" s="3" t="inlineStr"/>
+      <c r="K31" s="3" t="inlineStr"/>
+      <c r="L31" s="3" t="inlineStr"/>
+      <c r="M31" s="3" t="inlineStr"/>
+      <c r="N31" s="3" t="inlineStr"/>
+      <c r="O31" s="3" t="inlineStr"/>
+      <c r="P31" s="3" t="inlineStr"/>
+      <c r="Q31" s="3" t="inlineStr"/>
+      <c r="R31" s="3" t="inlineStr"/>
+      <c r="S31" s="3" t="inlineStr"/>
+      <c r="T31" s="3" t="inlineStr"/>
+      <c r="U31" s="3" t="inlineStr"/>
+      <c r="V31" s="3" t="inlineStr"/>
+      <c r="W31" s="3" t="inlineStr"/>
+      <c r="X31" s="3" t="inlineStr"/>
+      <c r="Y31" s="3" t="inlineStr"/>
+      <c r="Z31" s="3" t="inlineStr"/>
+      <c r="AA31" s="3" t="inlineStr"/>
+      <c r="AB31" s="3" t="inlineStr"/>
+      <c r="AC31" s="3" t="inlineStr"/>
+      <c r="AD31" s="3" t="inlineStr"/>
+      <c r="AE31" s="3" t="inlineStr"/>
+      <c r="AF31" s="3" t="inlineStr"/>
+      <c r="AG31" s="3" t="inlineStr"/>
+      <c r="AH31" s="3" t="inlineStr"/>
+      <c r="AI31" s="3" t="inlineStr"/>
+      <c r="AJ31" s="3" t="inlineStr"/>
+      <c r="AK31" s="3" t="inlineStr"/>
+      <c r="AL31" s="3" t="inlineStr"/>
+      <c r="AM31" s="3" t="inlineStr"/>
+      <c r="AN31" s="3" t="inlineStr"/>
+      <c r="AO31" s="3" t="inlineStr"/>
+      <c r="AP31" s="3" t="inlineStr"/>
+      <c r="AQ31" s="3" t="inlineStr"/>
+      <c r="AR31" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS31" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT31" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU31" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV31" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW31" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX31" s="3" t="inlineStr">
         <is>
           <t>Shashikant Chaudhary</t>
         </is>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_15_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_15_Oct_2026.xlsx
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>58.3%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>76.7%</t>
+          <t>77.4%</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>25.8%</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>9.7%</t>
         </is>
       </c>
     </row>
@@ -734,19 +734,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="C4" s="3" t="n">
-        <v>13</v>
-      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>92.9%</t>
+          <t>93.3%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>48.4%</t>
         </is>
       </c>
     </row>
@@ -817,13 +817,13 @@
         <v>2</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
@@ -993,13 +993,13 @@
         <v>5</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E10" s="4" t="n">
         <v>5</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -1013,7 +1013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX31"/>
+  <dimension ref="A1:AX32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1059,7 +1059,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -7040,6 +7040,222 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 4:39 PM</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr"/>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>TKT1371756</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>Rekha Thakula</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t>Rekha Thakula</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="inlineStr">
+        <is>
+          <t>9800685939</t>
+        </is>
+      </c>
+      <c r="P32" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q32" s="3" t="inlineStr"/>
+      <c r="R32" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 04:39:10 PM</t>
+        </is>
+      </c>
+      <c r="S32" s="3" t="inlineStr"/>
+      <c r="T32" s="3" t="inlineStr"/>
+      <c r="U32" s="3" t="inlineStr">
+        <is>
+          <t>9800685939</t>
+        </is>
+      </c>
+      <c r="V32" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 01:22:18 PM</t>
+        </is>
+      </c>
+      <c r="W32" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 04:39:10 PM</t>
+        </is>
+      </c>
+      <c r="X32" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y32" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z32" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA32" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB32" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC32" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD32" s="3" t="inlineStr"/>
+      <c r="AE32" s="3" t="inlineStr">
+        <is>
+          <t>Velpa Ganesh Temple M85M+9J6, Lalitpur , Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF32" s="3" t="inlineStr">
+        <is>
+          <t>asischand2074@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG32" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH32" s="3" t="inlineStr"/>
+      <c r="AI32" s="3" t="inlineStr">
+        <is>
+          <t>03:17 hour</t>
+        </is>
+      </c>
+      <c r="AJ32" s="3" t="inlineStr"/>
+      <c r="AK32" s="3" t="inlineStr"/>
+      <c r="AL32" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM32" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN32" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO32" s="3" t="inlineStr">
+        <is>
+          <t>1,11</t>
+        </is>
+      </c>
+      <c r="AP32" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ32" s="3" t="inlineStr"/>
+      <c r="AR32" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS32" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT32" s="3" t="inlineStr">
+        <is>
+          <t>3h 16m</t>
+        </is>
+      </c>
+      <c r="AU32" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV32" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW32" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX32" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_15_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_15_Oct_2026.xlsx
@@ -1059,7 +1059,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -7107,10 +7107,8 @@
           <t>Rekha Thakula</t>
         </is>
       </c>
-      <c r="O32" s="3" t="inlineStr">
-        <is>
-          <t>9800685939</t>
-        </is>
+      <c r="O32" s="3" t="n">
+        <v>9800685939</v>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
@@ -7204,25 +7202,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN32" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN32" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO32" s="3" t="inlineStr">
         <is>
           <t>1,11</t>
         </is>
       </c>
-      <c r="AP32" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP32" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ32" s="3" t="inlineStr"/>
       <c r="AR32" s="3" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS32" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_15_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_15_Oct_2026.xlsx
@@ -604,10 +604,10 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -688,10 +688,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
@@ -700,7 +700,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>25.8%</t>
+          <t>28.6%</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>8.6%</t>
         </is>
       </c>
     </row>
@@ -734,19 +734,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>93.3%</t>
+          <t>94.1%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>48.4%</t>
+          <t>48.6%</t>
         </is>
       </c>
     </row>
@@ -820,16 +820,16 @@
         <v>7</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Configuration Issue</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -842,16 +842,16 @@
         <v>0</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Configuration Issue</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -996,10 +996,10 @@
         <v>10</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1013,7 +1013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX32"/>
+  <dimension ref="A1:AX36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1024,7 +1024,7 @@
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="31" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
@@ -1059,7 +1059,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -7250,6 +7250,862 @@
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 5:59 PM</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr"/>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>TKT1370730</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>Anish Lama</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t>Anish Lama</t>
+        </is>
+      </c>
+      <c r="O33" s="3" t="inlineStr">
+        <is>
+          <t>9803069818</t>
+        </is>
+      </c>
+      <c r="P33" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q33" s="3" t="inlineStr"/>
+      <c r="R33" s="3" t="inlineStr">
+        <is>
+          <t>14 Oct 2026 03:33:09 PM</t>
+        </is>
+      </c>
+      <c r="S33" s="3" t="inlineStr"/>
+      <c r="T33" s="3" t="inlineStr"/>
+      <c r="U33" s="3" t="inlineStr">
+        <is>
+          <t>9803069818</t>
+        </is>
+      </c>
+      <c r="V33" s="3" t="inlineStr">
+        <is>
+          <t>14 Oct 2026 03:33:09 PM</t>
+        </is>
+      </c>
+      <c r="W33" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 05:59:00 PM</t>
+        </is>
+      </c>
+      <c r="X33" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y33" s="3" t="inlineStr">
+        <is>
+          <t>27.682899</t>
+        </is>
+      </c>
+      <c r="Z33" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA33" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB33" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC33" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD33" s="3" t="inlineStr"/>
+      <c r="AE33" s="3" t="inlineStr">
+        <is>
+          <t>Kirans brother newari  khajaghar, M6MM+C3R,  chandragiri, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF33" s="3" t="inlineStr"/>
+      <c r="AG33" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH33" s="3" t="inlineStr"/>
+      <c r="AI33" s="3" t="inlineStr">
+        <is>
+          <t>12:25 hour</t>
+        </is>
+      </c>
+      <c r="AJ33" s="3" t="inlineStr"/>
+      <c r="AK33" s="3" t="inlineStr"/>
+      <c r="AL33" s="3" t="inlineStr">
+        <is>
+          <t>Joshna Shrestha</t>
+        </is>
+      </c>
+      <c r="AM33" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN33" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO33" s="3" t="inlineStr">
+        <is>
+          <t>CDB449</t>
+        </is>
+      </c>
+      <c r="AP33" s="3" t="inlineStr">
+        <is>
+          <t>85.232973</t>
+        </is>
+      </c>
+      <c r="AQ33" s="3" t="inlineStr"/>
+      <c r="AR33" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS33" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 25m</t>
+        </is>
+      </c>
+      <c r="AT33" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 25m</t>
+        </is>
+      </c>
+      <c r="AU33" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV33" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW33" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX33" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 5:58 PM</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr"/>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>TKT1370730</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>Anish Lama</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t>Anish Lama</t>
+        </is>
+      </c>
+      <c r="O34" s="3" t="inlineStr">
+        <is>
+          <t>9803069818</t>
+        </is>
+      </c>
+      <c r="P34" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q34" s="3" t="inlineStr"/>
+      <c r="R34" s="3" t="inlineStr">
+        <is>
+          <t>14 Oct 2026 03:33:09 PM</t>
+        </is>
+      </c>
+      <c r="S34" s="3" t="inlineStr"/>
+      <c r="T34" s="3" t="inlineStr"/>
+      <c r="U34" s="3" t="inlineStr">
+        <is>
+          <t>9803069818</t>
+        </is>
+      </c>
+      <c r="V34" s="3" t="inlineStr">
+        <is>
+          <t>14 Oct 2026 03:33:09 PM</t>
+        </is>
+      </c>
+      <c r="W34" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 05:59:00 PM</t>
+        </is>
+      </c>
+      <c r="X34" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y34" s="3" t="inlineStr">
+        <is>
+          <t>27.682899</t>
+        </is>
+      </c>
+      <c r="Z34" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA34" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB34" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC34" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD34" s="3" t="inlineStr"/>
+      <c r="AE34" s="3" t="inlineStr">
+        <is>
+          <t>Kirans brother newari  khajaghar, M6MM+C3R,  chandragiri, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF34" s="3" t="inlineStr"/>
+      <c r="AG34" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH34" s="3" t="inlineStr"/>
+      <c r="AI34" s="3" t="inlineStr">
+        <is>
+          <t>12:25 hour</t>
+        </is>
+      </c>
+      <c r="AJ34" s="3" t="inlineStr"/>
+      <c r="AK34" s="3" t="inlineStr"/>
+      <c r="AL34" s="3" t="inlineStr">
+        <is>
+          <t>Joshna Shrestha</t>
+        </is>
+      </c>
+      <c r="AM34" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN34" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO34" s="3" t="inlineStr">
+        <is>
+          <t>CDB449</t>
+        </is>
+      </c>
+      <c r="AP34" s="3" t="inlineStr">
+        <is>
+          <t>85.232973</t>
+        </is>
+      </c>
+      <c r="AQ34" s="3" t="inlineStr"/>
+      <c r="AR34" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS34" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 25m</t>
+        </is>
+      </c>
+      <c r="AT34" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 25m</t>
+        </is>
+      </c>
+      <c r="AU34" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV34" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW34" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX34" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 5:57 PM</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr"/>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>Case : setupbox damage issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>setupbox damage issue</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>TKT1371462</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>Gita Panthi</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t>Gita Panthi</t>
+        </is>
+      </c>
+      <c r="O35" s="3" t="inlineStr">
+        <is>
+          <t>9841435071</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q35" s="3" t="inlineStr"/>
+      <c r="R35" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 10:09:01 AM</t>
+        </is>
+      </c>
+      <c r="S35" s="3" t="inlineStr"/>
+      <c r="T35" s="3" t="inlineStr"/>
+      <c r="U35" s="3" t="inlineStr">
+        <is>
+          <t>9841435071</t>
+        </is>
+      </c>
+      <c r="V35" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 09:54:20 AM</t>
+        </is>
+      </c>
+      <c r="W35" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 05:57:48 PM</t>
+        </is>
+      </c>
+      <c r="X35" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y35" s="3" t="inlineStr">
+        <is>
+          <t>27.689511</t>
+        </is>
+      </c>
+      <c r="Z35" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA35" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB35" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC35" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD35" s="3" t="inlineStr"/>
+      <c r="AE35" s="3" t="inlineStr">
+        <is>
+          <t>44600, Chandragiri 44600,Near Pokhrel Kirana Store, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF35" s="3" t="inlineStr">
+        <is>
+          <t>ganeshbarbot@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG35" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH35" s="3" t="inlineStr"/>
+      <c r="AI35" s="3" t="inlineStr">
+        <is>
+          <t>07:56 hour</t>
+        </is>
+      </c>
+      <c r="AJ35" s="3" t="inlineStr"/>
+      <c r="AK35" s="3" t="inlineStr"/>
+      <c r="AL35" s="3" t="inlineStr">
+        <is>
+          <t>Bhumika Saud</t>
+        </is>
+      </c>
+      <c r="AM35" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN35" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO35" s="3" t="inlineStr">
+        <is>
+          <t>CDB575</t>
+        </is>
+      </c>
+      <c r="AP35" s="3" t="inlineStr">
+        <is>
+          <t>85.24721</t>
+        </is>
+      </c>
+      <c r="AQ35" s="3" t="inlineStr"/>
+      <c r="AR35" s="3" t="inlineStr">
+        <is>
+          <t>Case : setupbox damage issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS35" s="3" t="inlineStr">
+        <is>
+          <t>7h 48m</t>
+        </is>
+      </c>
+      <c r="AT35" s="3" t="inlineStr">
+        <is>
+          <t>8h 3m</t>
+        </is>
+      </c>
+      <c r="AU35" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV35" s="3" t="inlineStr">
+        <is>
+          <t>Case : setupbox damage issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW35" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX35" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 5:56 PM</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr"/>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>Case : setupbox damage issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>setupbox damage issue</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>TKT1371462</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>Gita Panthi</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t>Gita Panthi</t>
+        </is>
+      </c>
+      <c r="O36" s="3" t="inlineStr">
+        <is>
+          <t>9841435071</t>
+        </is>
+      </c>
+      <c r="P36" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q36" s="3" t="inlineStr"/>
+      <c r="R36" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 10:09:01 AM</t>
+        </is>
+      </c>
+      <c r="S36" s="3" t="inlineStr"/>
+      <c r="T36" s="3" t="inlineStr"/>
+      <c r="U36" s="3" t="inlineStr">
+        <is>
+          <t>9841435071</t>
+        </is>
+      </c>
+      <c r="V36" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 09:54:20 AM</t>
+        </is>
+      </c>
+      <c r="W36" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 05:57:48 PM</t>
+        </is>
+      </c>
+      <c r="X36" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y36" s="3" t="inlineStr">
+        <is>
+          <t>27.689511</t>
+        </is>
+      </c>
+      <c r="Z36" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA36" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB36" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC36" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD36" s="3" t="inlineStr"/>
+      <c r="AE36" s="3" t="inlineStr">
+        <is>
+          <t>44600, Chandragiri 44600,Near Pokhrel Kirana Store, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF36" s="3" t="inlineStr">
+        <is>
+          <t>ganeshbarbot@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG36" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH36" s="3" t="inlineStr"/>
+      <c r="AI36" s="3" t="inlineStr">
+        <is>
+          <t>07:56 hour</t>
+        </is>
+      </c>
+      <c r="AJ36" s="3" t="inlineStr"/>
+      <c r="AK36" s="3" t="inlineStr"/>
+      <c r="AL36" s="3" t="inlineStr">
+        <is>
+          <t>Bhumika Saud</t>
+        </is>
+      </c>
+      <c r="AM36" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN36" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO36" s="3" t="inlineStr">
+        <is>
+          <t>CDB575</t>
+        </is>
+      </c>
+      <c r="AP36" s="3" t="inlineStr">
+        <is>
+          <t>85.24721</t>
+        </is>
+      </c>
+      <c r="AQ36" s="3" t="inlineStr"/>
+      <c r="AR36" s="3" t="inlineStr">
+        <is>
+          <t>Case : setupbox damage issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS36" s="3" t="inlineStr">
+        <is>
+          <t>7h 48m</t>
+        </is>
+      </c>
+      <c r="AT36" s="3" t="inlineStr">
+        <is>
+          <t>8h 3m</t>
+        </is>
+      </c>
+      <c r="AU36" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV36" s="3" t="inlineStr">
+        <is>
+          <t>Case : setupbox damage issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW36" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX36" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_15_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_15_Oct_2026.xlsx
@@ -1059,7 +1059,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -7317,10 +7317,8 @@
           <t>Anish Lama</t>
         </is>
       </c>
-      <c r="O33" s="3" t="inlineStr">
-        <is>
-          <t>9803069818</t>
-        </is>
+      <c r="O33" s="3" t="n">
+        <v>9803069818</v>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
@@ -7410,25 +7408,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN33" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN33" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO33" s="3" t="inlineStr">
         <is>
           <t>CDB449</t>
         </is>
       </c>
-      <c r="AP33" s="3" t="inlineStr">
-        <is>
-          <t>85.232973</t>
-        </is>
+      <c r="AP33" s="3" t="n">
+        <v>85.232973</v>
       </c>
       <c r="AQ33" s="3" t="inlineStr"/>
       <c r="AR33" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS33" s="3" t="inlineStr">
@@ -7529,10 +7523,8 @@
           <t>Anish Lama</t>
         </is>
       </c>
-      <c r="O34" s="3" t="inlineStr">
-        <is>
-          <t>9803069818</t>
-        </is>
+      <c r="O34" s="3" t="n">
+        <v>9803069818</v>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
@@ -7622,25 +7614,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN34" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN34" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO34" s="3" t="inlineStr">
         <is>
           <t>CDB449</t>
         </is>
       </c>
-      <c r="AP34" s="3" t="inlineStr">
-        <is>
-          <t>85.232973</t>
-        </is>
+      <c r="AP34" s="3" t="n">
+        <v>85.232973</v>
       </c>
       <c r="AQ34" s="3" t="inlineStr"/>
       <c r="AR34" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS34" s="3" t="inlineStr">
@@ -7741,10 +7729,8 @@
           <t>Gita Panthi</t>
         </is>
       </c>
-      <c r="O35" s="3" t="inlineStr">
-        <is>
-          <t>9841435071</t>
-        </is>
+      <c r="O35" s="3" t="n">
+        <v>9841435071</v>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
@@ -7838,25 +7824,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN35" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN35" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO35" s="3" t="inlineStr">
         <is>
           <t>CDB575</t>
         </is>
       </c>
-      <c r="AP35" s="3" t="inlineStr">
-        <is>
-          <t>85.24721</t>
-        </is>
+      <c r="AP35" s="3" t="n">
+        <v>85.24721</v>
       </c>
       <c r="AQ35" s="3" t="inlineStr"/>
       <c r="AR35" s="3" t="inlineStr">
         <is>
-          <t>Case : setupbox damage issue   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS35" s="3" t="inlineStr">
@@ -7957,10 +7939,8 @@
           <t>Gita Panthi</t>
         </is>
       </c>
-      <c r="O36" s="3" t="inlineStr">
-        <is>
-          <t>9841435071</t>
-        </is>
+      <c r="O36" s="3" t="n">
+        <v>9841435071</v>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
@@ -8054,25 +8034,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN36" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN36" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO36" s="3" t="inlineStr">
         <is>
           <t>CDB575</t>
         </is>
       </c>
-      <c r="AP36" s="3" t="inlineStr">
-        <is>
-          <t>85.24721</t>
-        </is>
+      <c r="AP36" s="3" t="n">
+        <v>85.24721</v>
       </c>
       <c r="AQ36" s="3" t="inlineStr"/>
       <c r="AR36" s="3" t="inlineStr">
         <is>
-          <t>Case : setupbox damage issue   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS36" s="3" t="inlineStr">
